--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>455.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.1%</t>
+          <t>-657.9%</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.3%</t>
+          <t>-192.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-119.1%</t>
+          <t>-120.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.3%</t>
+          <t>-226.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-65.1%</t>
         </is>
       </c>
     </row>
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.707815874244872</v>
+        <v>-3.713790990967976</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.979885220451461</v>
+        <v>1.97749517376222</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5195111890118949</v>
+        <v>0.5135360722887906</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.775074707870295</v>
+        <v>3.771489637836432</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.869384299772127</v>
+        <v>-3.875359416495231</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.913691860450712</v>
+        <v>1.91130181376147</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3867531484909112</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.697438963801719</v>
+        <v>3.693853893767857</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.001685591869681</v>
+        <v>-4.007660708592784</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.873844750477609</v>
+        <v>1.871454703788367</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3867531484909112</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.710512370667638</v>
+        <v>3.706927300633776</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.00324723468454</v>
+        <v>-4.009222351407644</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.873220093351665</v>
+        <v>1.870830046662423</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3867531484909112</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.710512370667638</v>
+        <v>3.706927300633776</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.031148021794013</v>
+        <v>-4.037123138517116</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.860583819634878</v>
+        <v>1.858193772945636</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3581313410710807</v>
+        <v>0.3521562243479764</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.688278257308879</v>
+        <v>3.684693187275017</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.153674124496907</v>
+        <v>-4.15964924122001</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.808337822530919</v>
+        <v>1.805947775841678</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2356052383681868</v>
+        <v>0.2296301216450826</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611527039664342</v>
+        <v>3.607941969630479</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.384188620682496</v>
+        <v>-4.390163737405599</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.782837983647187</v>
+        <v>1.780447936957946</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.005090742182598085</v>
+        <v>-0.0008843745405061609</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.539924301543492</v>
+        <v>3.53633923150963</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.640909438677319</v>
+        <v>-4.646884555400423</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.820461375451105</v>
+        <v>1.818071328761863</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.61518727605905</v>
+        <v>3.611602206025188</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.79489585645346</v>
+        <v>-4.800870973176564</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.827847077486289</v>
+        <v>1.825457030797047</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68416754520469</v>
+        <v>3.680582475170827</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.744373952625794</v>
+        <v>-4.750349069348898</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.834107041137476</v>
+        <v>1.831716994448234</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.670218747324811</v>
+        <v>3.666633677290948</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.996849106633518</v>
+        <v>-5.002824223356622</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.7449874685898</v>
+        <v>1.742597421900558</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.682089236380225</v>
+        <v>3.678504166346362</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.266321908555226</v>
+        <v>-5.272297025278331</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.638408882340061</v>
+        <v>1.636018835650818</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.683299770899168</v>
+        <v>3.679714700865306</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.423865980284668</v>
+        <v>-5.429841097007772</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.579512995875605</v>
+        <v>1.577122949186363</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1702256371014912</v>
+        <v>-0.1762007538245955</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.647280430042325</v>
+        <v>3.643695360008463</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.701830375867941</v>
+        <v>-5.707805492591046</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.463405090378485</v>
+        <v>1.461015043689243</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.2658204881100797</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.588586442207224</v>
+        <v>3.585001372173362</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.818798068506832</v>
+        <v>-5.824773185229937</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.578822070021973</v>
+        <v>1.576432023332731</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.2658204881100797</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.750790498906268</v>
+        <v>3.747205428872406</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.903516010727786</v>
+        <v>-5.90949112745089</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539781531097406</v>
+        <v>1.537391484408164</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3449614003150219</v>
+        <v>-0.3509365170381261</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.694567519513255</v>
+        <v>3.690982449479392</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.985450828996669</v>
+        <v>-5.991425945719773</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517237021358344</v>
+        <v>1.514846974669102</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3548961459021021</v>
+        <v>-0.3608712626252063</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.698836089729498</v>
+        <v>3.695251019695635</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.087426951245076</v>
+        <v>-6.093402067968181</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.485372210914883</v>
+        <v>1.482982164225641</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4568722681505096</v>
+        <v>-0.4628473848736139</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.646576054836355</v>
+        <v>3.642990984802493</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.977420667767855</v>
+        <v>-5.983395784490959</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.521527611549947</v>
+        <v>1.519137564860705</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4336676962332344</v>
+        <v>-0.4396428129563387</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.652651685230896</v>
+        <v>3.649066615197034</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.83436109202693</v>
+        <v>-5.840336208750034</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.583001452568292</v>
+        <v>1.58061140587905</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4256542696432551</v>
+        <v>-0.4316293863663594</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.661709751906858</v>
+        <v>3.658124681872995</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.532914366555092</v>
+        <v>-5.538889483278196</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.710841025639563</v>
+        <v>1.70845097895032</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.1301826608945221</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.849838670072496</v>
+        <v>3.846253600038634</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.557504610790276</v>
+        <v>-5.56347972751338</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.701976105698199</v>
+        <v>1.699586059008957</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.1301826608945221</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.850809847825206</v>
+        <v>3.847224777791344</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.506466234783756</v>
+        <v>-5.51244135150686</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.723234360480563</v>
+        <v>1.720844313791321</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.1301826608945221</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.851652752204962</v>
+        <v>3.8480676821711</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.465326939917125</v>
+        <v>-5.471302056640229</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.758728177301361</v>
+        <v>1.756338130612118</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.08306824930478707</v>
+        <v>-0.08904336602789131</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.895374427999086</v>
+        <v>3.891789357965223</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.354720799837523</v>
+        <v>-5.360695916560627</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.619154629457136</v>
+        <v>1.616764582767894</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.02753789077481494</v>
+        <v>0.0215627740517107</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.777922108170781</v>
+        <v>3.774337038136919</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.485301534368365</v>
+        <v>-5.49127665109147</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.570424379718763</v>
+        <v>1.568034333029521</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.1090179604791318</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.70307571152624</v>
+        <v>3.699490641492377</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.320805200177404</v>
+        <v>-5.326780316900508</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.62064973247123</v>
+        <v>1.618259685781988</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.1090179604791318</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.687502530602322</v>
+        <v>3.68391746056846</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.196324719453452</v>
+        <v>-5.202299836176556</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.66962963519724</v>
+        <v>1.667239588507998</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.1090179604791318</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.686690241038752</v>
+        <v>3.68310517100489</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.206709914343342</v>
+        <v>-5.212685031066446</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.675344336366357</v>
+        <v>1.672954289677115</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1134280386459169</v>
+        <v>-0.1194031553690211</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.690327903229891</v>
+        <v>3.686742833196028</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.1159554383147</v>
+        <v>-5.121930555037804</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.782483132554239</v>
+        <v>1.780093085864997</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.0286486793403794</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.815617594623501</v>
+        <v>3.812032524589639</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.74266642564581</v>
+        <v>3.796677306272424</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.965139284077774</v>
+        <v>-4.962983650754399</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.839678605067308</v>
+        <v>1.840540858396657</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.0286486793403794</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.8124866054418</v>
+        <v>3.808901535407937</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.9%</t>
+          <t>-675.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.2%</t>
+          <t>-199.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-120.1%</t>
+          <t>-119.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.9%</t>
+          <t>-226.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-65.1%</t>
+          <t>-64.8%</t>
         </is>
       </c>
     </row>
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.713790990967976</v>
+        <v>-3.707815874244872</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.97749517376222</v>
+        <v>1.979885220451461</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5135360722887906</v>
+        <v>0.5195111890118949</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.771489637836432</v>
+        <v>3.775074707870295</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.875359416495231</v>
+        <v>-3.869384299772127</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.91130181376147</v>
+        <v>1.913691860450712</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3867531484909112</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.693853893767857</v>
+        <v>3.697438963801719</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.007660708592784</v>
+        <v>-4.001685591869681</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.871454703788367</v>
+        <v>1.873844750477609</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3867531484909112</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.706927300633776</v>
+        <v>3.710512370667638</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.009222351407644</v>
+        <v>-4.00324723468454</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.870830046662423</v>
+        <v>1.873220093351665</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3867531484909112</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.706927300633776</v>
+        <v>3.710512370667638</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.037123138517116</v>
+        <v>-4.031148021794013</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.858193772945636</v>
+        <v>1.860583819634878</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3521562243479764</v>
+        <v>0.3581313410710807</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.684693187275017</v>
+        <v>3.688278257308879</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.15964924122001</v>
+        <v>-4.153674124496907</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.805947775841678</v>
+        <v>1.808337822530919</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2296301216450826</v>
+        <v>0.2356052383681868</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.607941969630479</v>
+        <v>3.611527039664342</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.390163737405599</v>
+        <v>-4.384188620682496</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.780447936957946</v>
+        <v>1.782837983647187</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.0008843745405061609</v>
+        <v>0.005090742182598085</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.53633923150963</v>
+        <v>3.539924301543492</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.646884555400423</v>
+        <v>-4.640909438677319</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.818071328761863</v>
+        <v>1.820461375451105</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.611602206025188</v>
+        <v>3.61518727605905</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.800870973176564</v>
+        <v>-4.79489585645346</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.825457030797047</v>
+        <v>1.827847077486289</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.680582475170827</v>
+        <v>3.68416754520469</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.750349069348898</v>
+        <v>-4.744373952625794</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.831716994448234</v>
+        <v>1.834107041137476</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.666633677290948</v>
+        <v>3.670218747324811</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.002824223356622</v>
+        <v>-4.996849106633518</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.742597421900558</v>
+        <v>1.7449874685898</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.678504166346362</v>
+        <v>3.682089236380225</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.272297025278331</v>
+        <v>-5.266321908555226</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.636018835650818</v>
+        <v>1.638408882340061</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.679714700865306</v>
+        <v>3.683299770899168</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.429841097007772</v>
+        <v>-5.423865980284668</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.577122949186363</v>
+        <v>1.579512995875605</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1762007538245955</v>
+        <v>-0.1702256371014912</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.643695360008463</v>
+        <v>3.647280430042325</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.707805492591046</v>
+        <v>-5.701830375867941</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.461015043689243</v>
+        <v>1.463405090378485</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2658204881100797</v>
+        <v>-0.2598453713869755</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.585001372173362</v>
+        <v>3.588586442207224</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.824773185229937</v>
+        <v>-5.818798068506832</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.576432023332731</v>
+        <v>1.578822070021973</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2658204881100797</v>
+        <v>-0.2598453713869755</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.747205428872406</v>
+        <v>3.750790498906268</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.90949112745089</v>
+        <v>-5.903516010727786</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.537391484408164</v>
+        <v>1.539781531097406</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3509365170381261</v>
+        <v>-0.3449614003150219</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.690982449479392</v>
+        <v>3.694567519513255</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.991425945719773</v>
+        <v>-5.985450828996669</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.514846974669102</v>
+        <v>1.517237021358344</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3608712626252063</v>
+        <v>-0.3548961459021021</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.695251019695635</v>
+        <v>3.698836089729498</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.093402067968181</v>
+        <v>-6.087426951245076</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.482982164225641</v>
+        <v>1.485372210914883</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4628473848736139</v>
+        <v>-0.4568722681505096</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.642990984802493</v>
+        <v>3.646576054836355</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.983395784490959</v>
+        <v>-5.977420667767855</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.519137564860705</v>
+        <v>1.521527611549947</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4396428129563387</v>
+        <v>-0.4336676962332344</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.649066615197034</v>
+        <v>3.652651685230896</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.840336208750034</v>
+        <v>-5.83436109202693</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.58061140587905</v>
+        <v>1.583001452568292</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4316293863663594</v>
+        <v>-0.4256542696432551</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.658124681872995</v>
+        <v>3.661709751906858</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.538889483278196</v>
+        <v>-5.532914366555092</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.70845097895032</v>
+        <v>1.710841025639563</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1301826608945221</v>
+        <v>-0.1242075441714179</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.846253600038634</v>
+        <v>3.849838670072496</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.56347972751338</v>
+        <v>-5.557504610790276</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.699586059008957</v>
+        <v>1.701976105698199</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1301826608945221</v>
+        <v>-0.1242075441714179</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.847224777791344</v>
+        <v>3.850809847825206</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.51244135150686</v>
+        <v>-5.506466234783756</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.720844313791321</v>
+        <v>1.723234360480563</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1301826608945221</v>
+        <v>-0.1242075441714179</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.8480676821711</v>
+        <v>3.851652752204962</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.471302056640229</v>
+        <v>-5.465326939917125</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.756338130612118</v>
+        <v>1.758728177301361</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.08904336602789131</v>
+        <v>-0.08306824930478707</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.891789357965223</v>
+        <v>3.895374427999086</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.360695916560627</v>
+        <v>-5.354720799837523</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.616764582767894</v>
+        <v>1.619154629457136</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.0215627740517107</v>
+        <v>0.02753789077481494</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.774337038136919</v>
+        <v>3.777922108170781</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.49127665109147</v>
+        <v>-5.485301534368365</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.568034333029521</v>
+        <v>1.570424379718763</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1090179604791318</v>
+        <v>-0.1030428437560276</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.699490641492377</v>
+        <v>3.70307571152624</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.326780316900508</v>
+        <v>-5.320805200177404</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.618259685781988</v>
+        <v>1.62064973247123</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1090179604791318</v>
+        <v>-0.1030428437560276</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.68391746056846</v>
+        <v>3.687502530602322</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.202299836176556</v>
+        <v>-5.356382151516108</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.667239588507998</v>
+        <v>1.605606662372178</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1090179604791318</v>
+        <v>-0.1030428437560276</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.68310517100489</v>
+        <v>3.686690241038752</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.212685031066446</v>
+        <v>-5.366767346405998</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.672954289677115</v>
+        <v>1.611321363541295</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1194031553690211</v>
+        <v>-0.1134280386459169</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.686742833196028</v>
+        <v>3.690327903229891</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.121930555037804</v>
+        <v>-5.276012870377356</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.780093085864997</v>
+        <v>1.718460159729176</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.0286486793403794</v>
+        <v>-0.02267356261727516</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.812032524589639</v>
+        <v>3.815617594623501</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.796677306272424</v>
+        <v>3.732072224270321</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.962983650754399</v>
+        <v>-5.134296122562951</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.840540858396657</v>
+        <v>1.772015869673237</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.0286486793403794</v>
+        <v>-0.02267356261727516</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.808901535407937</v>
+        <v>3.8124866054418</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.0%</t>
+          <t>-674.4%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24649.7%</t>
+          <t>-24638.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-199.0%</t>
+          <t>-198.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-119.1%</t>
+          <t>-125.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.3%</t>
+          <t>-226.9%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-73.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2039"/>
+  <dimension ref="A1:G2040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.707815874244872</v>
+        <v>-3.713790990967976</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.979885220451461</v>
+        <v>1.97749517376222</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5195111890118949</v>
+        <v>0.5135360722887906</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.775074707870295</v>
+        <v>3.771489637836432</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.869384299772127</v>
+        <v>-3.875359416495231</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.913691860450712</v>
+        <v>1.91130181376147</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3867531484909112</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.697438963801719</v>
+        <v>3.693853893767857</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.001685591869681</v>
+        <v>-4.007660708592784</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.873844750477609</v>
+        <v>1.871454703788367</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3867531484909112</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.710512370667638</v>
+        <v>3.706927300633776</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.00324723468454</v>
+        <v>-4.009222351407644</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.873220093351665</v>
+        <v>1.870830046662423</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3867531484909112</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.710512370667638</v>
+        <v>3.706927300633776</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.031148021794013</v>
+        <v>-4.037123138517116</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.860583819634878</v>
+        <v>1.858193772945636</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3581313410710807</v>
+        <v>0.3521562243479764</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.688278257308879</v>
+        <v>3.684693187275017</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.153674124496907</v>
+        <v>-4.15964924122001</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.808337822530919</v>
+        <v>1.805947775841678</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2356052383681868</v>
+        <v>0.2296301216450826</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611527039664342</v>
+        <v>3.607941969630479</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.384188620682496</v>
+        <v>-4.390163737405599</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.782837983647187</v>
+        <v>1.780447936957946</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.005090742182598085</v>
+        <v>-0.0008843745405061609</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.539924301543492</v>
+        <v>3.53633923150963</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.640909438677319</v>
+        <v>-4.646884555400423</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.820461375451105</v>
+        <v>1.818071328761863</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.61518727605905</v>
+        <v>3.611602206025188</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.79489585645346</v>
+        <v>-4.800870973176564</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.827847077486289</v>
+        <v>1.825457030797047</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68416754520469</v>
+        <v>3.680582475170827</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.744373952625794</v>
+        <v>-4.750349069348898</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.834107041137476</v>
+        <v>1.831716994448234</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.670218747324811</v>
+        <v>3.666633677290948</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.996849106633518</v>
+        <v>-5.002824223356622</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.7449874685898</v>
+        <v>1.742597421900558</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.682089236380225</v>
+        <v>3.678504166346362</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.266321908555226</v>
+        <v>-5.272297025278331</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.638408882340061</v>
+        <v>1.636018835650818</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.109298948684321</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.683299770899168</v>
+        <v>3.679714700865306</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.423865980284668</v>
+        <v>-5.429841097007772</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.579512995875605</v>
+        <v>1.577122949186363</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1702256371014912</v>
+        <v>-0.1762007538245955</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.647280430042325</v>
+        <v>3.643695360008463</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.701830375867941</v>
+        <v>-5.707805492591046</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.463405090378485</v>
+        <v>1.461015043689243</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.2658204881100797</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.588586442207224</v>
+        <v>3.585001372173362</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.818798068506832</v>
+        <v>-5.824773185229937</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.578822070021973</v>
+        <v>1.576432023332731</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.2658204881100797</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.750790498906268</v>
+        <v>3.747205428872406</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.903516010727786</v>
+        <v>-5.90949112745089</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539781531097406</v>
+        <v>1.537391484408164</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3449614003150219</v>
+        <v>-0.3509365170381261</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.694567519513255</v>
+        <v>3.690982449479392</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.985450828996669</v>
+        <v>-5.991425945719773</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517237021358344</v>
+        <v>1.514846974669102</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3548961459021021</v>
+        <v>-0.3608712626252063</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.698836089729498</v>
+        <v>3.695251019695635</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.087426951245076</v>
+        <v>-6.093402067968181</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.485372210914883</v>
+        <v>1.482982164225641</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4568722681505096</v>
+        <v>-0.4628473848736139</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.646576054836355</v>
+        <v>3.642990984802493</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.977420667767855</v>
+        <v>-5.983395784490959</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.521527611549947</v>
+        <v>1.519137564860705</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4336676962332344</v>
+        <v>-0.4396428129563387</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.652651685230896</v>
+        <v>3.649066615197034</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.83436109202693</v>
+        <v>-5.840336208750034</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.583001452568292</v>
+        <v>1.58061140587905</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4256542696432551</v>
+        <v>-0.4316293863663594</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.661709751906858</v>
+        <v>3.658124681872995</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.532914366555092</v>
+        <v>-5.538889483278196</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.710841025639563</v>
+        <v>1.70845097895032</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.1301826608945221</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.849838670072496</v>
+        <v>3.846253600038634</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.557504610790276</v>
+        <v>-5.56347972751338</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.701976105698199</v>
+        <v>1.699586059008957</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.1301826608945221</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.850809847825206</v>
+        <v>3.847224777791344</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.506466234783756</v>
+        <v>-5.51244135150686</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.723234360480563</v>
+        <v>1.720844313791321</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.1301826608945221</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.851652752204962</v>
+        <v>3.8480676821711</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.465326939917125</v>
+        <v>-5.471302056640229</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.758728177301361</v>
+        <v>1.756338130612118</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.08306824930478707</v>
+        <v>-0.08904336602789131</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.895374427999086</v>
+        <v>3.891789357965223</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.354720799837523</v>
+        <v>-5.360695916560627</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.619154629457136</v>
+        <v>1.616764582767894</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.02753789077481494</v>
+        <v>0.0215627740517107</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.777922108170781</v>
+        <v>3.774337038136919</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.485301534368365</v>
+        <v>-5.49127665109147</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.570424379718763</v>
+        <v>1.568034333029521</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.1090179604791318</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.70307571152624</v>
+        <v>3.699490641492377</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.320805200177404</v>
+        <v>-5.326780316900508</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.62064973247123</v>
+        <v>1.618259685781988</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.1090179604791318</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.687502530602322</v>
+        <v>3.68391746056846</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.356382151516108</v>
+        <v>-5.350608466885107</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.605606662372178</v>
+        <v>1.607916136224578</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.1090179604791318</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.686690241038752</v>
+        <v>3.68310517100489</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.366767346405998</v>
+        <v>-5.360993661774996</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.611321363541295</v>
+        <v>1.613630837393695</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1134280386459169</v>
+        <v>-0.1194031553690211</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.690327903229891</v>
+        <v>3.686742833196028</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.276012870377356</v>
+        <v>-5.270239185746354</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.718460159729176</v>
+        <v>1.720769633581577</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.0286486793403794</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.815617594623501</v>
+        <v>3.812032524589639</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,45 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.732072224270321</v>
+        <v>3.855134695881694</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.134296122562951</v>
+        <v>-5.12852243793195</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.772015869673237</v>
+        <v>1.774325343525637</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.0286486793403794</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.8124866054418</v>
+        <v>3.808901535407937</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="2" t="n">
+        <v>45502</v>
+      </c>
+      <c r="B2040" t="n">
+        <v>3.734568551328294</v>
+      </c>
+      <c r="C2040" t="n">
+        <v>3.729657239463256</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>-5.12852243793195</v>
+      </c>
+      <c r="E2040" t="n">
+        <v>1.774325343525637</v>
+      </c>
+      <c r="F2040" t="n">
+        <v>-0.0286486793403794</v>
+      </c>
+      <c r="G2040" t="n">
+        <v>3.722721036449624</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-674.4%</t>
+          <t>-675.0%</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-198.8%</t>
+          <t>-199.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.2%</t>
+          <t>-124.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.9%</t>
+          <t>-226.3%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.713790990967976</v>
+        <v>-3.707815874244872</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.97749517376222</v>
+        <v>1.979885220451461</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5135360722887906</v>
+        <v>0.5195111890118949</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.771489637836432</v>
+        <v>3.775074707870295</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.875359416495231</v>
+        <v>-3.869384299772127</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.91130181376147</v>
+        <v>1.913691860450712</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3867531484909112</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.693853893767857</v>
+        <v>3.697438963801719</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.007660708592784</v>
+        <v>-4.001685591869681</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.871454703788367</v>
+        <v>1.873844750477609</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3867531484909112</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.706927300633776</v>
+        <v>3.710512370667638</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.009222351407644</v>
+        <v>-4.00324723468454</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.870830046662423</v>
+        <v>1.873220093351665</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3867531484909112</v>
+        <v>0.3927282652140155</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.706927300633776</v>
+        <v>3.710512370667638</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.037123138517116</v>
+        <v>-4.031148021794013</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.858193772945636</v>
+        <v>1.860583819634878</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3521562243479764</v>
+        <v>0.3581313410710807</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.684693187275017</v>
+        <v>3.688278257308879</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.15964924122001</v>
+        <v>-4.153674124496907</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.805947775841678</v>
+        <v>1.808337822530919</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2296301216450826</v>
+        <v>0.2356052383681868</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.607941969630479</v>
+        <v>3.611527039664342</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.390163737405599</v>
+        <v>-4.384188620682496</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.780447936957946</v>
+        <v>1.782837983647187</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.0008843745405061609</v>
+        <v>0.005090742182598085</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.53633923150963</v>
+        <v>3.539924301543492</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.646884555400423</v>
+        <v>-4.640909438677319</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.818071328761863</v>
+        <v>1.820461375451105</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.611602206025188</v>
+        <v>3.61518727605905</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.800870973176564</v>
+        <v>-4.79489585645346</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.825457030797047</v>
+        <v>1.827847077486289</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.680582475170827</v>
+        <v>3.68416754520469</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.750349069348898</v>
+        <v>-4.744373952625794</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.831716994448234</v>
+        <v>1.834107041137476</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.666633677290948</v>
+        <v>3.670218747324811</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.002824223356622</v>
+        <v>-4.996849106633518</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.742597421900558</v>
+        <v>1.7449874685898</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.678504166346362</v>
+        <v>3.682089236380225</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.272297025278331</v>
+        <v>-5.266321908555226</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.636018835650818</v>
+        <v>1.638408882340061</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.109298948684321</v>
+        <v>-0.1033238319612167</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.679714700865306</v>
+        <v>3.683299770899168</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.429841097007772</v>
+        <v>-5.423865980284668</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.577122949186363</v>
+        <v>1.579512995875605</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1762007538245955</v>
+        <v>-0.1702256371014912</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.643695360008463</v>
+        <v>3.647280430042325</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.707805492591046</v>
+        <v>-5.701830375867941</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.461015043689243</v>
+        <v>1.463405090378485</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2658204881100797</v>
+        <v>-0.2598453713869755</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.585001372173362</v>
+        <v>3.588586442207224</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.824773185229937</v>
+        <v>-5.818798068506832</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.576432023332731</v>
+        <v>1.578822070021973</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2658204881100797</v>
+        <v>-0.2598453713869755</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.747205428872406</v>
+        <v>3.750790498906268</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.90949112745089</v>
+        <v>-5.903516010727786</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.537391484408164</v>
+        <v>1.539781531097406</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3509365170381261</v>
+        <v>-0.3449614003150219</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.690982449479392</v>
+        <v>3.694567519513255</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.991425945719773</v>
+        <v>-5.985450828996669</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.514846974669102</v>
+        <v>1.517237021358344</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3608712626252063</v>
+        <v>-0.3548961459021021</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.695251019695635</v>
+        <v>3.698836089729498</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.093402067968181</v>
+        <v>-6.087426951245076</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.482982164225641</v>
+        <v>1.485372210914883</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4628473848736139</v>
+        <v>-0.4568722681505096</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.642990984802493</v>
+        <v>3.646576054836355</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.983395784490959</v>
+        <v>-5.977420667767855</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.519137564860705</v>
+        <v>1.521527611549947</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4396428129563387</v>
+        <v>-0.4336676962332344</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.649066615197034</v>
+        <v>3.652651685230896</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.78557808520366</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.840336208750034</v>
+        <v>-5.83436109202693</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.58061140587905</v>
+        <v>1.583001452568292</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4316293863663594</v>
+        <v>-0.4256542696432551</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.658124681872995</v>
+        <v>3.661709751906858</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436926</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.538889483278196</v>
+        <v>-5.532914366555092</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.70845097895032</v>
+        <v>1.710841025639563</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1301826608945221</v>
+        <v>-0.1242075441714179</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.846253600038634</v>
+        <v>3.849838670072496</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.56347972751338</v>
+        <v>-5.557504610790276</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.699586059008957</v>
+        <v>1.701976105698199</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1301826608945221</v>
+        <v>-0.1242075441714179</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.847224777791344</v>
+        <v>3.850809847825206</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.51244135150686</v>
+        <v>-5.506466234783756</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.720844313791321</v>
+        <v>1.723234360480563</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1301826608945221</v>
+        <v>-0.1242075441714179</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.8480676821711</v>
+        <v>3.851652752204962</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354682</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.471302056640229</v>
+        <v>-5.465326939917125</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.756338130612118</v>
+        <v>1.758728177301361</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.08904336602789131</v>
+        <v>-0.08306824930478707</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.891789357965223</v>
+        <v>3.895374427999086</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085619</v>
+        <v>3.825767093085617</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.360695916560627</v>
+        <v>-5.354720799837523</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.616764582767894</v>
+        <v>1.619154629457136</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.0215627740517107</v>
+        <v>0.02753789077481494</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.774337038136919</v>
+        <v>3.777922108170781</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462781</v>
+        <v>3.804703121462779</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.49127665109147</v>
+        <v>-5.485301534368365</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.568034333029521</v>
+        <v>1.570424379718763</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1090179604791318</v>
+        <v>-0.1030428437560276</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.699490641492377</v>
+        <v>3.70307571152624</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775043021218597</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.326780316900508</v>
+        <v>-5.320805200177404</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.618259685781988</v>
+        <v>1.62064973247123</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1090179604791318</v>
+        <v>-0.1030428437560276</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.68391746056846</v>
+        <v>3.687502530602322</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462766</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.350608466885107</v>
+        <v>-5.356382151516108</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.607916136224578</v>
+        <v>1.605606662372178</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1090179604791318</v>
+        <v>-0.1030428437560276</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.68310517100489</v>
+        <v>3.686690241038752</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.832321184533047</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.360993661774996</v>
+        <v>-5.366767346405998</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.613630837393695</v>
+        <v>1.611321363541295</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1194031553690211</v>
+        <v>-0.1134280386459169</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.686742833196028</v>
+        <v>3.690327903229891</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120423</v>
+        <v>3.834429654120421</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.270239185746354</v>
+        <v>-5.276012870377356</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.720769633581577</v>
+        <v>1.718460159729176</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.0286486793403794</v>
+        <v>-0.02267356261727516</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.812032524589639</v>
+        <v>3.815617594623501</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881694</v>
+        <v>3.855134695881692</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.12852243793195</v>
+        <v>-5.134296122562951</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.774325343525637</v>
+        <v>1.772015869673237</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.0286486793403794</v>
+        <v>-0.02267356261727516</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.808901535407937</v>
+        <v>3.8124866054418</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,19 +48465,19 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.734568551328294</v>
+        <v>3.734568551328293</v>
       </c>
       <c r="C2040" t="n">
         <v>3.729657239463256</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.12852243793195</v>
+        <v>-5.134296122562951</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.774325343525637</v>
+        <v>1.772015869673237</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.0286486793403794</v>
+        <v>-0.02267356261727516</v>
       </c>
       <c r="G2040" t="n">
         <v>3.722721036449624</v>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>453.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.0%</t>
+          <t>-663.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24638.1%</t>
+          <t>-24637.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-199.0%</t>
+          <t>-194.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-65.2%</t>
         </is>
       </c>
     </row>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.001685591869681</v>
+        <v>-4.049815343753984</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.873844750477609</v>
+        <v>1.854592849723887</v>
       </c>
       <c r="F2011" t="n">
         <v>0.3927282652140155</v>
@@ -47827,10 +47827,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.00324723468454</v>
+        <v>-4.051376986568844</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.873220093351665</v>
+        <v>1.853968192597944</v>
       </c>
       <c r="F2012" t="n">
         <v>0.3927282652140155</v>
@@ -47850,10 +47850,10 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.031148021794013</v>
+        <v>-4.079277773678316</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.860583819634878</v>
+        <v>1.841331918881157</v>
       </c>
       <c r="F2013" t="n">
         <v>0.3581313410710807</v>
@@ -47873,10 +47873,10 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.153674124496907</v>
+        <v>-4.20180387638121</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.808337822530919</v>
+        <v>1.789085921777198</v>
       </c>
       <c r="F2014" t="n">
         <v>0.2356052383681868</v>
@@ -47896,10 +47896,10 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.384188620682496</v>
+        <v>-4.432318372566799</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.782837983647187</v>
+        <v>1.763586082893466</v>
       </c>
       <c r="F2015" t="n">
         <v>0.005090742182598085</v>
@@ -47919,10 +47919,10 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.640909438677319</v>
+        <v>-4.689039190561623</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.820461375451105</v>
+        <v>1.801209474697384</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.1033238319612167</v>
@@ -47942,10 +47942,10 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.79489585645346</v>
+        <v>-4.843025608337763</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.827847077486289</v>
+        <v>1.808595176732567</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.1033238319612167</v>
@@ -47965,10 +47965,10 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.744373952625794</v>
+        <v>-4.792503704510097</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.834107041137476</v>
+        <v>1.814855140383755</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.1033238319612167</v>
@@ -47988,10 +47988,10 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.996849106633518</v>
+        <v>-5.044978858517822</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.7449874685898</v>
+        <v>1.725735567836079</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.1033238319612167</v>
@@ -48011,10 +48011,10 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.266321908555226</v>
+        <v>-5.31445166043953</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.638408882340061</v>
+        <v>1.619156981586339</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.1033238319612167</v>
@@ -48034,10 +48034,10 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.423865980284668</v>
+        <v>-5.471995732168971</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.579512995875605</v>
+        <v>1.560261095121884</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.1702256371014912</v>
@@ -48057,10 +48057,10 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.701830375867941</v>
+        <v>-5.749960127752245</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.463405090378485</v>
+        <v>1.444153189624764</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.2598453713869755</v>
@@ -48080,10 +48080,10 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.818798068506832</v>
+        <v>-5.866927820391136</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.578822070021973</v>
+        <v>1.559570169268252</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.2598453713869755</v>
@@ -48103,10 +48103,10 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.903516010727786</v>
+        <v>-5.951645762612089</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539781531097406</v>
+        <v>1.520529630343685</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.3449614003150219</v>
@@ -48126,10 +48126,10 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.985450828996669</v>
+        <v>-6.033580580880972</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517237021358344</v>
+        <v>1.497985120604622</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.3548961459021021</v>
@@ -48149,10 +48149,10 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.087426951245076</v>
+        <v>-6.13555670312938</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.485372210914883</v>
+        <v>1.466120310161162</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.4568722681505096</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.977420667767855</v>
+        <v>-6.025550419652158</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.521527611549947</v>
+        <v>1.502275710796226</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.4336676962332344</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78557808520366</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.83436109202693</v>
+        <v>-5.882490843911233</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.583001452568292</v>
+        <v>1.56374955181457</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.4256542696432551</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436926</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.532914366555092</v>
+        <v>-5.581044118439396</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.710841025639563</v>
+        <v>1.691589124885841</v>
       </c>
       <c r="F2029" t="n">
         <v>-0.1242075441714179</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.557504610790276</v>
+        <v>-5.605634362674579</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.701976105698199</v>
+        <v>1.682724204944478</v>
       </c>
       <c r="F2030" t="n">
         <v>-0.1242075441714179</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.506466234783756</v>
+        <v>-5.554595986668059</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.723234360480563</v>
+        <v>1.703982459726841</v>
       </c>
       <c r="F2031" t="n">
         <v>-0.1242075441714179</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354682</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.465326939917125</v>
+        <v>-5.513456691801428</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.758728177301361</v>
+        <v>1.739476276547639</v>
       </c>
       <c r="F2032" t="n">
         <v>-0.08306824930478707</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085617</v>
+        <v>3.825767093085619</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.354720799837523</v>
+        <v>-5.402850551721826</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.619154629457136</v>
+        <v>1.599902728703415</v>
       </c>
       <c r="F2033" t="n">
         <v>0.02753789077481494</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462779</v>
+        <v>3.804703121462781</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.485301534368365</v>
+        <v>-5.533431286252669</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.570424379718763</v>
+        <v>1.551172478965041</v>
       </c>
       <c r="F2034" t="n">
         <v>-0.1030428437560276</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218597</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.320805200177404</v>
+        <v>-5.368934952061707</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.62064973247123</v>
+        <v>1.601397831717509</v>
       </c>
       <c r="F2035" t="n">
         <v>-0.1030428437560276</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462766</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.356382151516108</v>
+        <v>-5.244454471337756</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.605606662372178</v>
+        <v>1.650377734443519</v>
       </c>
       <c r="F2036" t="n">
         <v>-0.1030428437560276</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533047</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.366767346405998</v>
+        <v>-5.254839666227645</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.611321363541295</v>
+        <v>1.656092435612635</v>
       </c>
       <c r="F2037" t="n">
         <v>-0.1134280386459169</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120421</v>
+        <v>3.834429654120423</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.276012870377356</v>
+        <v>-5.164085190199003</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.718460159729176</v>
+        <v>1.763231231800517</v>
       </c>
       <c r="F2038" t="n">
         <v>-0.02267356261727516</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881692</v>
+        <v>3.855134695881693</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.134296122562951</v>
+        <v>-5.022368442384598</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.772015869673237</v>
+        <v>1.816786941744578</v>
       </c>
       <c r="F2039" t="n">
         <v>-0.02267356261727516</v>
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.734568551328293</v>
+        <v>3.793075500228949</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.729657239463256</v>
+        <v>3.815241167004015</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.134296122562951</v>
+        <v>-5.022368442384598</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.772015869673237</v>
+        <v>1.816786941744578</v>
       </c>
       <c r="F2040" t="n">
         <v>-0.02267356261727516</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.722721036449624</v>
+        <v>3.808304963990383</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.7%</t>
+          <t>449.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-663.8%</t>
+          <t>-677.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24637.9%</t>
+          <t>-24837.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.5%</t>
+          <t>-200.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-267.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.6%</t>
+          <t>-123.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.3%</t>
+          <t>-246.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-160.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-65.2%</t>
+          <t>-86.2%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43785,10 +43785,10 @@
         <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.119052324986328</v>
       </c>
     </row>
     <row r="1837">
@@ -43808,10 +43808,10 @@
         <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.119541463712203</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43831,10 +43831,10 @@
         <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.041754512197421</v>
       </c>
     </row>
     <row r="1839">
@@ -43854,10 +43854,10 @@
         <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.076695596694964</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43877,10 +43877,10 @@
         <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.587618356407115</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.108659710640092</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43900,10 +43900,10 @@
         <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>3.933089671438995</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43923,10 +43923,10 @@
         <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>3.934107280569465</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43946,10 +43946,10 @@
         <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>3.924735312557221</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43969,10 +43969,10 @@
         <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>3.931039382556141</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -43992,10 +43992,10 @@
         <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>3.935804699389843</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44015,10 +44015,10 @@
         <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.405815606229521</v>
+        <v>1.368849131759997</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.962642922183679</v>
+        <v>3.940463037501964</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44038,10 +44038,10 @@
         <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>0.9510951082131597</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.687737514878926</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44061,10 +44061,10 @@
         <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.702052808321955</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44084,10 +44084,10 @@
         <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.70694495287588</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44107,10 +44107,10 @@
         <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>0.9129984917923695</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.664719362517286</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44130,10 +44130,10 @@
         <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.5469297646477168</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.438162425536944</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44153,10 +44153,10 @@
         <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.3384389831960324</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.333406246404702</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44176,10 +44176,10 @@
         <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.3585923366948448</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.353597008912558</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.059272384141832</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44222,10 +44222,10 @@
         <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.057814922954695</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44245,10 +44245,10 @@
         <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.09752997149878867</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.081341678307589</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44268,10 +44268,10 @@
         <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>2.953540670831634</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44291,10 +44291,10 @@
         <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>2.955313597531894</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44314,10 +44314,10 @@
         <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.4404592448270772</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.859795987134538</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44337,10 +44337,10 @@
         <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.434122977597822</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.851882522474182</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.5020539630867268</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.809704522836804</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.4216084539930649</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.864459388527242</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.7179192382920774</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.685927432953667</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.439535710660019</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.434721143131479</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.432715193740357</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44498,10 +44498,10 @@
         <v>0.3558145575154041</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.442973884409036</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>0.2146107148038916</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.439073449554731</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.1937345079619548</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.437478369609732</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44567,10 +44567,10 @@
         <v>0.07884894716708413</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.195251151206634</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.400011464098613</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>0.0001347593089597865</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.195251151206634</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.395985159564209</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.1531678975096762</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.195251151206634</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.395883058242625</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.1523909596188013</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.199737596408023</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.395762707093223</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.2908527853223521</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.199737596408023</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.401113010391272</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-0.3030763907468632</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.250086659862245</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.378819592275917</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.3390823510936527</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.347705937283642</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.323289776444848</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44728,10 +44728,10 @@
         <v>-0.3578173945754242</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.401777436792001</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.293740433061404</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.934927838825567</v>
+        <v>-8.943751556884919</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4340074675887271</v>
+        <v>-0.4375369548124679</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.568132080654555</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.199440843862514</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.968580677334041</v>
+        <v>-8.977404395393393</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4429860485076804</v>
+        <v>-0.4465155357314212</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.668545448571592</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.143675377596728</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.895110845666592</v>
+        <v>-8.903934563725944</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3982264143472798</v>
+        <v>-0.4017559015710206</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.595075616904144</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.203128978090618</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.070235263053135</v>
+        <v>-9.079058981112487</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4537209605543806</v>
+        <v>-0.4572504477781214</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.770200034290688</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.112609548406208</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.304687357067625</v>
+        <v>-9.313511075126977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5547209630617722</v>
+        <v>-0.558250450285513</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.770200034290688</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.105390383504613</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.409062088094071</v>
+        <v>-9.417885806153423</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.603143046246327</v>
+        <v>-0.6066725334700678</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.874574765317133</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.036093354114769</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.461848243694398</v>
+        <v>-9.47067196175375</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6231417186479016</v>
+        <v>-0.6266712058716424</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.970250251899531</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.979803852003887</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.587885037062687</v>
+        <v>-9.596708755122039</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6708627073661027</v>
+        <v>-0.6743921945898435</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.944998629089788</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>1.997648554318847</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.530813265166756</v>
+        <v>-9.539636983226108</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6440436629213293</v>
+        <v>-0.6475731501450701</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.944998629089788</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.001638890005248</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.672485106890877</v>
+        <v>-9.681308824950229</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7021876265097191</v>
+        <v>-0.7057171137334599</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.944998629089788</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.000163663106506</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.622894262466042</v>
+        <v>-9.631717980525394</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6672978785749133</v>
+        <v>-0.6708273657986541</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.895407784664954</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.044971579926279</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.473975927994186</v>
+        <v>-9.482799646053538</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6207816784328535</v>
+        <v>-0.6243111656565943</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.864158193929781</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.0506702007207</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.248130775274774</v>
+        <v>-9.256954493334128</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5208645443088802</v>
+        <v>-0.5243940315326214</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.822231518342618</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.085405279109207</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.123552118937182</v>
+        <v>-9.132375836996536</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4698939372177846</v>
+        <v>-0.4734234244415259</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.822231518342618</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.086544423665265</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.176447406981469</v>
+        <v>-9.185271125040822</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4884182782733912</v>
+        <v>-0.4919477654971329</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.817276172254171</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.092151405480441</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.104314231693587</v>
+        <v>-9.113137949752941</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4538313039196025</v>
+        <v>-0.4573607911433442</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.817276172254171</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.097885109719077</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.03294783908394</v>
+        <v>-9.041771557143294</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4350220092696087</v>
+        <v>-0.4385514964933503</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.745909779644524</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.130967682891001</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.939488805098716</v>
+        <v>-8.948312523158069</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4075218769884263</v>
+        <v>-0.411051364212168</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.745909779644524</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.121084201578094</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.928835623545284</v>
+        <v>-8.937659341604638</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4050951648664278</v>
+        <v>-0.4086246520901691</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.745909779644524</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.11924964107872</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.830928584868794</v>
+        <v>-8.839752302928147</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3662326643692921</v>
+        <v>-0.3697621515930338</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.677924029783967</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.159740776021593</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.806975043892836</v>
+        <v>-8.815798761952189</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3559827418334156</v>
+        <v>-0.3595122290571569</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.65397048880801</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.174781406752661</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.542915105570039</v>
+        <v>-8.551738823629393</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2636190826660489</v>
+        <v>-0.2671485698897902</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.389910550485213</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.319957053584586</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.835835482065201</v>
+        <v>-7.844659200124554</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01642573307558548</v>
+        <v>0.01289624585184423</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.389910550485213</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.317170019924285</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.79565118369901</v>
+        <v>-7.804474901758364</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.03284307630990302</v>
+        <v>0.02931358908616177</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.349726252119023</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.341624222831841</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.632251312759648</v>
+        <v>-7.641075030819001</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09756984590640494</v>
+        <v>0.09404035868266369</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.18632638117966</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.439030966616216</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.398770090530049</v>
+        <v>-7.407593808589403</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1988867636360969</v>
+        <v>0.1953572764123552</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9528451589500615</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.587044128791827</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.249103699522534</v>
+        <v>-7.257927417581888</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2558611097261436</v>
+        <v>0.2523316225024024</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8599416677075256</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.63989401322439</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.116828225891648</v>
+        <v>-7.125651943951001</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3041387859255251</v>
+        <v>0.3006092987017839</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7276661940766389</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.714626784149949</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.961089893331906</v>
+        <v>-6.969913611391259</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3692491796370589</v>
+        <v>0.3657196924133173</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5719278615168973</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.81088484437343</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712090094648325</v>
+        <v>-6.720913812707678</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4817554403341497</v>
+        <v>0.4782259531104085</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2472458891152278</v>
+        <v>-0.3229280628333167</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.018600369038091</v>
+        <v>2.973191064807237</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.817680084421429</v>
+        <v>-6.826503802480783</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3115435148256895</v>
+        <v>0.3080140276019478</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3528358788883322</v>
+        <v>-0.428518052606421</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.827270445575009</v>
+        <v>2.781861141344156</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.836414986540026</v>
+        <v>-6.84523870459938</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3525938958553372</v>
+        <v>0.3490644086315955</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3584318885484635</v>
+        <v>-0.4341140622665523</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.872457181656017</v>
+        <v>2.827047877425164</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.688474945132427</v>
+        <v>-6.697298663191781</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2918909897302093</v>
+        <v>0.2883615025064676</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3381109726399059</v>
+        <v>-0.4137931463579947</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.764770808512984</v>
+        <v>2.719361504282131</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.635505422878438</v>
+        <v>-6.644329140937792</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3043648123783265</v>
+        <v>0.3008353251545848</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.3608236241040059</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.787838535611899</v>
+        <v>2.742429231381046</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.591957016107748</v>
+        <v>-6.600780734167102</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3148235629915095</v>
+        <v>0.3112940757677678</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.3608236241040059</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.780877923516806</v>
+        <v>2.735468619285953</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.558593809628979</v>
+        <v>-6.567417527688333</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3426311999641598</v>
+        <v>0.3391017127404186</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.3608236241040059</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.795340277897949</v>
+        <v>2.749930973667096</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.450334672506457</v>
+        <v>-6.459158390565811</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3804669752723635</v>
+        <v>0.3769374880486223</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.3608236241040059</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.789872398357144</v>
+        <v>2.744463094126291</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.327043537689327</v>
+        <v>-6.33586725574868</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4272815232097931</v>
+        <v>0.4237520359860514</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1618503155687865</v>
+        <v>-0.2375324892868754</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.861345173257999</v>
+        <v>2.815935869027146</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.305894338785883</v>
+        <v>-6.314718056845237</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4434421810084954</v>
+        <v>0.4399126937847537</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.216383290383432</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88173567083739</v>
+        <v>2.836326366606537</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.062128896802439</v>
+        <v>-6.070952614861793</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5367290661489239</v>
+        <v>0.5331995789251822</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.216383290383432</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.877516379184441</v>
+        <v>2.832107074953588</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.960366076525144</v>
+        <v>-5.969189794584498</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5795585081798578</v>
+        <v>0.5760290209561165</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.2031642219910033</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.887572134139914</v>
+        <v>2.842162829909061</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.710515682576069</v>
+        <v>-5.719339400635423</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6722407407431898</v>
+        <v>0.6687112535194482</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.2031642219910033</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.880314209123616</v>
+        <v>2.834904904892763</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.534623590108637</v>
+        <v>-5.543447308167991</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7461967012508115</v>
+        <v>0.7426672140270698</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.2031642219910033</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.883913332644265</v>
+        <v>2.838504028413412</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.363177127086174</v>
+        <v>-5.372000845145528</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8281027925143505</v>
+        <v>0.8245733052906088</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04396441474954865</v>
+        <v>-0.03171775896854018</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.000108716512297</v>
+        <v>2.954699412281443</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.288887561347835</v>
+        <v>-5.297711279407189</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8568390964259831</v>
+        <v>0.8533096092022414</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1182539804878879</v>
+        <v>0.0425718067697991</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.043702933571597</v>
+        <v>2.998293629340744</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.2252518191139</v>
+        <v>-5.234075537173254</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.886988194373874</v>
+        <v>0.8834587071501327</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.1062075490037336</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.086579179966275</v>
+        <v>3.041169875735422</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.11382505978798</v>
+        <v>-5.122648777847334</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.912753156888038</v>
+        <v>0.9092236696642964</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.1062075490037336</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.067773438750071</v>
+        <v>3.022364134519218</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.124327682853269</v>
+        <v>-5.133151400912623</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9102951842867997</v>
+        <v>0.906765697063058</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1713870996565336</v>
+        <v>0.09570492593844476</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.063214941535775</v>
+        <v>3.017805637304922</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.052085114682074</v>
+        <v>-5.060908832741428</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9431215253900977</v>
+        <v>0.9395920381663561</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1713870996565336</v>
+        <v>0.09570492593844476</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.067144255370595</v>
+        <v>3.021734951139742</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034371427804209</v>
+        <v>-5.043195145863563</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9508855840585837</v>
+        <v>0.9473560968348425</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1745684285534504</v>
+        <v>0.09888625483536156</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.069731636626085</v>
+        <v>3.024322332395232</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.925566542324482</v>
+        <v>-4.934390260383836</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9914056094704682</v>
+        <v>0.9878761222467267</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1745684285534504</v>
+        <v>0.09888625483536156</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.066729707846079</v>
+        <v>3.021320403615225</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.705545744287472</v>
+        <v>-4.714369462346825</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.080992965695887</v>
+        <v>1.077463478472145</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3157882736214306</v>
+        <v>0.2401060999033418</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.153040651897481</v>
+        <v>3.107631347666628</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.572678055224194</v>
+        <v>-4.581501773283548</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.150034224123021</v>
+        <v>1.146504736899279</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3157882736214306</v>
+        <v>0.2401060999033418</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.168934834699304</v>
+        <v>3.123525530468451</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.452504971859695</v>
+        <v>-4.461328689919049</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.199249301909122</v>
+        <v>1.195719814685381</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4359613569859296</v>
+        <v>0.3602791832678408</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.242184529158306</v>
+        <v>3.196775224927452</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.307832826759958</v>
+        <v>-4.316656544819311</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.267206262510457</v>
+        <v>1.263676775286716</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.580633502085667</v>
+        <v>0.5049513283675782</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.339075918779588</v>
+        <v>3.293666614548735</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36770765411765</v>
+        <v>-4.376531372177004</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.229293822968806</v>
+        <v>1.225764335745064</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5207586747279749</v>
+        <v>0.445076501009886</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.289188513766399</v>
+        <v>3.243779209535545</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.247887423206813</v>
+        <v>-4.256711141266167</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.292511084567349</v>
+        <v>1.288981597343608</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5207586747279749</v>
+        <v>0.445076501009886</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.304477683000607</v>
+        <v>3.259068378769754</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.250357129668619</v>
+        <v>-4.259180847727973</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.199167401305068</v>
+        <v>1.195637914081327</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5182889682661687</v>
+        <v>0.4426067945480799</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.210640058445965</v>
+        <v>3.165230754215111</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.318727315992629</v>
+        <v>-4.327551034051983</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.091081188260766</v>
+        <v>1.087551701037024</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.4518824935842948</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.135467339352995</v>
+        <v>3.090058035122142</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.332515368839676</v>
+        <v>-4.34133908689903</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.076002675753838</v>
+        <v>1.072473188530097</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.4518824935842948</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.125904047984887</v>
+        <v>3.080494743754033</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.388035444732266</v>
+        <v>-4.396859162791619</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.190825482089005</v>
+        <v>1.187295994865263</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.4518824935842948</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.262934884677089</v>
+        <v>3.217525580446236</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.212561184939796</v>
+        <v>-4.22138490299915</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.265582417997781</v>
+        <v>1.262052930774039</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.4518824935842948</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.267502116668877</v>
+        <v>3.222092812438023</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.323497437581045</v>
+        <v>-4.332321155640399</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.196949945702488</v>
+        <v>1.193420458478747</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.4518824935842948</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.243244145430084</v>
+        <v>3.197834841199231</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.289833892108763</v>
+        <v>-4.298657610168116</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.138953677292851</v>
+        <v>1.135424190069109</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.4855460390565767</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.191980586114902</v>
+        <v>3.146571281884049</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.229981272905039</v>
+        <v>-4.238804990964393</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.173067111406472</v>
+        <v>1.169537624182731</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.4855460390565767</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.202152972547035</v>
+        <v>3.156743668316182</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.143737809878662</v>
+        <v>-4.152561527938015</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.202510767190884</v>
+        <v>1.198981279967142</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.4855460390565767</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.197099243120896</v>
+        <v>3.151689938890042</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.189044629277642</v>
+        <v>-4.197868347336995</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.176163814875817</v>
+        <v>1.172634327652076</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5204180497654347</v>
+        <v>0.4447358760473459</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.164388920759882</v>
+        <v>3.118979616529029</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.218077733979943</v>
+        <v>-4.226901452039296</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.165102446027999</v>
+        <v>1.161572958804257</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5204180497654347</v>
+        <v>0.4447358760473459</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.164940793792984</v>
+        <v>3.119531489562131</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.125267252529083</v>
+        <v>-4.134090970588437</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.131499330499708</v>
+        <v>1.127969843275967</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6132285312162941</v>
+        <v>0.5375463574982052</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.149899774554865</v>
+        <v>3.104490470324012</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.169656721858511</v>
+        <v>-4.178480439917864</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.115617018692538</v>
+        <v>1.112087531468796</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5688390618868664</v>
+        <v>0.4931568881687776</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.12513956888181</v>
+        <v>3.079730264650956</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.286198326963853</v>
+        <v>-4.295022045023207</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.064076085162124</v>
+        <v>1.060546597938382</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4522974567815236</v>
+        <v>0.3766152830634348</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.050290314330327</v>
+        <v>3.004881010099473</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.17382132578118</v>
+        <v>-4.182645043840534</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.11451818146586</v>
+        <v>1.110988694242119</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4522974567815236</v>
+        <v>0.3766152830634348</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.055781610160994</v>
+        <v>3.010372305930141</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.201601723682533</v>
+        <v>-4.210425441741886</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.114903224073858</v>
+        <v>1.111373736850117</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4245170588801706</v>
+        <v>0.3488348851620817</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.050610573188721</v>
+        <v>3.005201268957868</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.319982396412671</v>
+        <v>-4.328806114472025</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9059066749824563</v>
+        <v>0.9023771877587148</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.2816170330111055</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.848635581898789</v>
+        <v>2.803226277667935</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.428596474856002</v>
+        <v>-4.437420192915356</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9826107043243293</v>
+        <v>0.9790812171005878</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.2816170330111055</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.968785242617995</v>
+        <v>2.923375938387141</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.393187436607859</v>
+        <v>-4.402011154667213</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.01128734572591</v>
+        <v>1.007757858502168</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.2816170330111055</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.983298268720318</v>
+        <v>2.937888964489464</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.354803774049708</v>
+        <v>-4.363627492109062</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.024060252091539</v>
+        <v>1.020530764867797</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3956828692873455</v>
+        <v>0.3200006955692567</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.003747907597577</v>
+        <v>2.958338603366724</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.177687444014542</v>
+        <v>-4.186511162073896</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.091635812950907</v>
+        <v>1.088106325727165</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3956828692873455</v>
+        <v>0.3200006955692567</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.000476936442879</v>
+        <v>2.955067632212026</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.222779688848088</v>
+        <v>-4.231603406907442</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.074282306779402</v>
+        <v>1.07075281955566</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3337868261179557</v>
+        <v>0.2581046523998669</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.964022702303158</v>
+        <v>2.918613398072305</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.04340426760932</v>
+        <v>-4.052227985668674</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.139819450581323</v>
+        <v>1.136289963357582</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4905635842886744</v>
+        <v>0.4148814105705856</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.051875732512003</v>
+        <v>3.00646642828115</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.088418481129926</v>
+        <v>-4.09724219918928</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.102621220504671</v>
+        <v>1.099091733280929</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4602146889740698</v>
+        <v>0.384532515255981</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.01447385065483</v>
+        <v>2.969064546423977</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.355422991402361</v>
+        <v>-4.364246709461715</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.001510978734642</v>
+        <v>0.9979814915109009</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2658516509311212</v>
+        <v>0.1901694772130324</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.903547590168007</v>
+        <v>2.858138285937154</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.456620772839534</v>
+        <v>-4.465444490898888</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9602357880562749</v>
+        <v>0.9567063008325332</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.197442837385802</v>
+        <v>0.1217606636677132</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.861706223937317</v>
+        <v>2.816296919706464</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.450109806225221</v>
+        <v>-4.458933524284575</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9604401362563166</v>
+        <v>0.9569106490325749</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.197442837385802</v>
+        <v>0.1217606636677132</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.859306185491634</v>
+        <v>2.813896881260781</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.431071678517924</v>
+        <v>-4.439895396577278</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9645801065474804</v>
+        <v>0.9610506193237389</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1392592260546075</v>
+        <v>0.06357705233651867</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.820920737901162</v>
+        <v>2.775511433670309</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.462198309668542</v>
+        <v>-4.471022027727896</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.071423855721423</v>
+        <v>1.067894368497682</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1392592260546075</v>
+        <v>0.06357705233651867</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.940215139535352</v>
+        <v>2.894805835304499</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.47606507100246</v>
+        <v>-4.484888789061814</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.06671048017399</v>
+        <v>1.063180992950248</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1014013093207846</v>
+        <v>0.02571913560269573</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.918333718481192</v>
+        <v>2.872924414250339</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.43126089946253</v>
+        <v>-4.440084617521884</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.090640679186888</v>
+        <v>1.087111191963146</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1014013093207846</v>
+        <v>0.02571913560269573</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.924342248878118</v>
+        <v>2.878932944647265</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.283517929227528</v>
+        <v>-4.292341647286881</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.047688088558088</v>
+        <v>1.044158601334347</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2692086665556677</v>
+        <v>0.1935264928375789</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.922976884496248</v>
+        <v>2.877567580265394</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.367339150502226</v>
+        <v>-4.37616286856158</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.01695322157969</v>
+        <v>1.013423734355948</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2692086665556677</v>
+        <v>0.1935264928375789</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.925770506027729</v>
+        <v>2.880361201796875</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.361186444449442</v>
+        <v>-4.370010162508795</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.020076652392462</v>
+        <v>1.01654716516872</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.275361372608452</v>
+        <v>0.1996791988903632</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.930124478051057</v>
+        <v>2.884715173820204</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.377995742599944</v>
+        <v>-4.386819460659297</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.012433409872371</v>
+        <v>1.00890392264863</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2585520744579504</v>
+        <v>0.1828699007398615</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.919119375900867</v>
+        <v>2.873710071670013</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.315697743823821</v>
+        <v>-4.324521461883175</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.103688163179641</v>
+        <v>1.1001586759559</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2585520744579504</v>
+        <v>0.1828699007398615</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.985454929697688</v>
+        <v>2.940045625466834</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.113907546158663</v>
+        <v>-4.122731264218017</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9866962439598315</v>
+        <v>0.98316675673609</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4565702666271048</v>
+        <v>0.3808880929090159</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.906557846713307</v>
+        <v>2.861148542482454</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.164794258844858</v>
+        <v>-4.173617976904212</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.036631791207529</v>
+        <v>1.033102303983787</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4056835539409102</v>
+        <v>0.3300013802228214</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.946316051423766</v>
+        <v>2.900906747192912</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.262534803469832</v>
+        <v>-4.271358521529186</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.012163309473583</v>
+        <v>1.008633822249841</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.38979427580793</v>
+        <v>0.3141121020898412</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.951410220660021</v>
+        <v>2.906000916429168</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.322744101475117</v>
+        <v>-4.331567819534471</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9866155710961404</v>
+        <v>0.9830860838723989</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3295849778026455</v>
+        <v>0.2539028040845567</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.913820622681522</v>
+        <v>2.868411318450669</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.246322055043191</v>
+        <v>-4.255145773102544</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.01567600770884</v>
+        <v>1.012146520485098</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3295849778026455</v>
+        <v>0.2539028040845567</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.912312240721451</v>
+        <v>2.866902936490598</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.201948923404622</v>
+        <v>-4.210772641463976</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.033288127799703</v>
+        <v>1.029758640575962</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3739581094412141</v>
+        <v>0.2982759357231253</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.938798987140028</v>
+        <v>2.893389682909175</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.224429274263507</v>
+        <v>-4.233252992322861</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.01868978159474</v>
+        <v>1.015160294370998</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3739581094412141</v>
+        <v>0.2982759357231253</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.933192781278619</v>
+        <v>2.887783477047766</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.176773543702451</v>
+        <v>-4.185597261761805</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.044133830846967</v>
+        <v>1.040604343623225</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4216138400022698</v>
+        <v>0.3459316662841809</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.968167976643056</v>
+        <v>2.922758672412203</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.076255385203696</v>
+        <v>-4.08507910326305</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.089233467621193</v>
+        <v>1.085703980397452</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5221319985010243</v>
+        <v>0.4464498247829355</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.033371245117034</v>
+        <v>2.987961940886181</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.136921975606086</v>
+        <v>-4.14574569366544</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.05172150393611</v>
+        <v>1.048192016712368</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4404336817824906</v>
+        <v>0.3647515080644018</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.971106927561786</v>
+        <v>2.925697623330933</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.092083573997687</v>
+        <v>-4.100907292057041</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.073754567190098</v>
+        <v>1.070225079966356</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4449771147273601</v>
+        <v>0.3692949410092713</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.977930689939337</v>
+        <v>2.932521385708483</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.111582030239695</v>
+        <v>-4.120405748299049</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.070116124324373</v>
+        <v>1.066586637100631</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3968924734474558</v>
+        <v>0.321210299729367</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.953240844802472</v>
+        <v>2.907831540571618</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.067379193153795</v>
+        <v>-4.076202911213149</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.09367686168657</v>
+        <v>1.090147374462829</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4410953105333563</v>
+        <v>0.3654131368152674</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.985642149581849</v>
+        <v>2.940232845350996</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.104358220817238</v>
+        <v>-4.113181938876592</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.07729525109044</v>
+        <v>1.073765763866699</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4780692123246868</v>
+        <v>0.402387038606598</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.006236491125895</v>
+        <v>2.960827186895042</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.946066803277966</v>
+        <v>-3.954890521337319</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.191859583289189</v>
+        <v>1.188330096065447</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4780692123246868</v>
+        <v>0.402387038606598</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.057484256308935</v>
+        <v>3.012074952078081</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.738424799643489</v>
+        <v>-3.747248517702843</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.273357089337233</v>
+        <v>1.269827602113491</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.685711215959163</v>
+        <v>0.6100290422410741</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.180510163083873</v>
+        <v>3.13510085885302</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.687392706920961</v>
+        <v>-3.696216424980315</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.288718154664514</v>
+        <v>1.285188667440772</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7367433086816909</v>
+        <v>0.6610611349636021</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.20607764695566</v>
+        <v>3.160668342724807</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.622168525793755</v>
+        <v>-3.630992243853109</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.331995231208101</v>
+        <v>1.328465743984359</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8019674898088965</v>
+        <v>0.7262853160908077</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.262399559724689</v>
+        <v>3.216990255493835</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.584741505722622</v>
+        <v>-3.593565223781976</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.342927011535835</v>
+        <v>1.339397524312093</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8072190278380782</v>
+        <v>0.7315368541199894</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.261511454841478</v>
+        <v>3.216102150610625</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.60485316175733</v>
+        <v>-3.613676879816684</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.336139141453192</v>
+        <v>1.33260965422945</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8182463728354974</v>
+        <v>0.7425641991174086</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.26938465417117</v>
+        <v>3.223975349940317</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.551108347330125</v>
+        <v>-3.559932065389479</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.518194838245285</v>
+        <v>1.514665351021543</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8283096822759594</v>
+        <v>0.7526275085578705</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.435980410856658</v>
+        <v>3.390571106625805</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.476326086305113</v>
+        <v>-3.485149804364466</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.668220651873107</v>
+        <v>1.664691164649365</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.903091943300972</v>
+        <v>0.8274097695828831</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.600962676689483</v>
+        <v>3.555553372458629</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.450242002041305</v>
+        <v>-3.459065720100658</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.670362261592489</v>
+        <v>1.666832774368747</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.903091943300972</v>
+        <v>0.8274097695828831</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.592670652703342</v>
+        <v>3.547261348472488</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.372110821192358</v>
+        <v>-3.380934539251712</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.699807929515847</v>
+        <v>1.696278442292106</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9772687541846565</v>
+        <v>0.9015865804665677</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.635369934817332</v>
+        <v>3.589960630586479</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.363218359799075</v>
+        <v>-3.372042077858429</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.720919319799952</v>
+        <v>1.71738983257621</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9772687541846565</v>
+        <v>0.9015865804665677</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.652924340544123</v>
+        <v>3.60751503631327</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.531694476768953</v>
+        <v>-3.540518194828306</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.645383920416585</v>
+        <v>1.641854433192843</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9493209184680758</v>
+        <v>0.8736387447499869</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.628010686518759</v>
+        <v>3.582601382287905</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.833894947907369</v>
+        <v>-2.842718665966723</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.90577342914908</v>
+        <v>1.902243941925338</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8789728590976651</v>
+        <v>0.8032906853795763</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.567071548084374</v>
+        <v>3.521662243853521</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.811173844224217</v>
+        <v>-2.819997562283571</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.905525893119245</v>
+        <v>1.901996405895504</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8789728590976651</v>
+        <v>0.8032906853795763</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.557735570581279</v>
+        <v>3.512326266350425</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.940375657518259</v>
+        <v>-2.949199375577613</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.012751293652797</v>
+        <v>2.009221806429056</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7497710458036229</v>
+        <v>0.674088872085534</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.639120608456023</v>
+        <v>3.593711304225169</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.095156664296515</v>
+        <v>-3.103980382355869</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.987916713435141</v>
+        <v>1.9843872262114</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7164033717491467</v>
+        <v>0.6407211980310579</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.656177826516983</v>
+        <v>3.61076852228613</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.088101974081341</v>
+        <v>-3.096925692140695</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.987413945510756</v>
+        <v>1.983884458287015</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7234580619643205</v>
+        <v>0.6477758882462317</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.657085996635633</v>
+        <v>3.611676692404779</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.061150749754853</v>
+        <v>-3.069974467814207</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.008200588886093</v>
+        <v>2.004671101662352</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.6626562342739508</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.676020357897006</v>
+        <v>3.630611053666152</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.19710375781117</v>
+        <v>-3.205927475870523</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.137922517808526</v>
+        <v>2.134393030584785</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.6626562342739508</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.860123490041965</v>
+        <v>3.814714185811112</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.219511875616042</v>
+        <v>-3.228335593675395</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.12107596558957</v>
+        <v>2.117546478365829</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7383384079920396</v>
+        <v>0.6626562342739508</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.852240184944959</v>
+        <v>3.806830880714105</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.367517643095441</v>
+        <v>-3.376341361154795</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.063927658147448</v>
+        <v>2.060398170923706</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6516113991284982</v>
+        <v>0.5759292254104094</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.802257979176471</v>
+        <v>3.756848674945618</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.376958568983971</v>
+        <v>-3.385782287043325</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.116405005513883</v>
+        <v>2.112875518290142</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7740385166718896</v>
+        <v>0.6983563429538008</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.931967967424353</v>
+        <v>3.8865586631935</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.429232176319613</v>
+        <v>-3.438055894378966</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.098386657124927</v>
+        <v>2.094857169901186</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7217649093362484</v>
+        <v>0.6460827356181595</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.903494897568269</v>
+        <v>3.858085593337416</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.505562153920518</v>
+        <v>-3.514385871979872</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.065966478978341</v>
+        <v>2.062436991754599</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7217649093362484</v>
+        <v>0.6460827356181595</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.901606710462044</v>
+        <v>3.856197406231191</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.707815874244872</v>
+        <v>-3.716639592304225</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.979885220451461</v>
+        <v>1.97635573322772</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5195111890118949</v>
+        <v>0.4438290152938061</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.775074707870295</v>
+        <v>3.729665403639441</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.869384299772127</v>
+        <v>-3.878208017831481</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.913691860450712</v>
+        <v>1.91016237322697</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3170460914959267</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.697438963801719</v>
+        <v>3.652029659570866</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.049815343753984</v>
+        <v>-4.010509309929034</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.854592849723887</v>
+        <v>1.870315263253867</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.3170460914959267</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.710512370667638</v>
+        <v>3.665103066436785</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.474875411539228</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.051376986568844</v>
+        <v>-4.184878598397765</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.853968192597944</v>
+        <v>1.792572744649315</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3927282652140155</v>
+        <v>0.1863569721406489</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.710512370667638</v>
+        <v>3.578694791606558</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.47339945266623</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.079277773678316</v>
+        <v>-4.212779385507238</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.841331918881157</v>
+        <v>1.779936470932528</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3581313410710807</v>
+        <v>0.1517600479977141</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.688278257308879</v>
+        <v>3.556460678247799</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.470163896643429</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.20180387638121</v>
+        <v>-4.335305488210132</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.789085921777198</v>
+        <v>1.727690473828569</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2356052383681868</v>
+        <v>0.02923394529482021</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611527039664342</v>
+        <v>3.479709460603261</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.536869856233933</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.432318372566799</v>
+        <v>-4.565819984395721</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.763586082893466</v>
+        <v>1.702190634944837</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.005090742182598085</v>
+        <v>-0.2012805508907685</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.539924301543492</v>
+        <v>3.408106722482412</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.67718157523578</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.689039190561623</v>
+        <v>-4.822540802390545</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.801209474697384</v>
+        <v>1.739814026748755</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.3096951250345834</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.61518727605905</v>
+        <v>3.48336969699797</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.74616184438142</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.843025608337763</v>
+        <v>-4.976527220166686</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.808595176732567</v>
+        <v>1.747199728783938</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.3096951250345834</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68416754520469</v>
+        <v>3.55234996614361</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.732213046501541</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.792503704510097</v>
+        <v>-4.92600531633902</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.814855140383755</v>
+        <v>1.753459692435125</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.3096951250345834</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.670218747324811</v>
+        <v>3.538401168263731</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.744083535556955</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.044978858517822</v>
+        <v>-5.178480470346744</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.725735567836079</v>
+        <v>1.664340119887449</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.3096951250345834</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.682089236380225</v>
+        <v>3.550271657319145</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.745294070075898</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.31445166043953</v>
+        <v>-5.447953272268452</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.619156981586339</v>
+        <v>1.55776153363771</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1033238319612167</v>
+        <v>-0.3096951250345834</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.683299770899168</v>
+        <v>3.551482191838089</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74941581230322</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.471995732168971</v>
+        <v>-5.605497343997894</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.560261095121884</v>
+        <v>1.498865647173255</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1702256371014912</v>
+        <v>-0.3765969301748578</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.647280430042325</v>
+        <v>3.515462850981245</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.744493665039409</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.749960127752245</v>
+        <v>-5.883461739581167</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.444153189624764</v>
+        <v>1.382757741676135</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.4662166644603421</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.588586442207224</v>
+        <v>3.456768863146144</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.906697721738453</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.866927820391136</v>
+        <v>-6.000429432220058</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.559570169268252</v>
+        <v>1.498174721319623</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2598453713869755</v>
+        <v>-0.4662166644603421</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.750790498906268</v>
+        <v>3.618972919845188</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.901544359702267</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.951645762612089</v>
+        <v>-6.085147374441012</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.520529630343685</v>
+        <v>1.459134182395055</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3449614003150219</v>
+        <v>-0.5513326933883884</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.694567519513255</v>
+        <v>3.562749940452175</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.911773777270759</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.033580580880972</v>
+        <v>-6.167082192709895</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.497985120604622</v>
+        <v>1.436589672655993</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3548961459021021</v>
+        <v>-0.5612674389754686</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.698836089729498</v>
+        <v>3.567018510668418</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783632867332687</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.920699415726661</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.13555670312938</v>
+        <v>-6.269058314958302</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.466120310161162</v>
+        <v>1.404724862212533</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4568722681505096</v>
+        <v>-0.6632435612238762</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.646576054836355</v>
+        <v>3.514758475775276</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.912852302970836</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.025550419652158</v>
+        <v>-6.159052031481081</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.502275710796226</v>
+        <v>1.440880262847597</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4336676962332344</v>
+        <v>-0.640038989306601</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.652651685230896</v>
+        <v>3.520834106169816</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.917102313692811</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.882490843911233</v>
+        <v>-6.015992455740156</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.56374955181457</v>
+        <v>1.502354103865941</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4256542696432551</v>
+        <v>-0.6320255627166217</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.661709751906858</v>
+        <v>3.529892172845778</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.924363196575347</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.581044118439396</v>
+        <v>-5.714545730268318</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.691589124885841</v>
+        <v>1.630193676937212</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.3305788372447844</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.849838670072496</v>
+        <v>3.718021091011416</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.925334374328057</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.605634362674579</v>
+        <v>-5.739135974503502</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.682724204944478</v>
+        <v>1.621328756995849</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.3305788372447844</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.850809847825206</v>
+        <v>3.718992268764127</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.926177278707812</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.554595986668059</v>
+        <v>-5.688097598496982</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.703982459726841</v>
+        <v>1.642587011778212</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1242075441714179</v>
+        <v>-0.3305788372447844</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.851652752204962</v>
+        <v>3.719835173143882</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.945215377581958</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.513456691801428</v>
+        <v>-5.646958303630351</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.739476276547639</v>
+        <v>1.67808082859901</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.08306824930478707</v>
+        <v>-0.2894395423781536</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.895374427999086</v>
+        <v>3.763556848938006</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085619</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.761399373705892</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.402850551721826</v>
+        <v>-5.536352163550749</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.599902728703415</v>
+        <v>1.538507280754786</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.02753789077481494</v>
+        <v>-0.1788334022985516</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.777922108170781</v>
+        <v>3.646104529109702</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462781</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.764901417779856</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.533431286252669</v>
+        <v>-5.666932898081591</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.551172478965041</v>
+        <v>1.489777031016412</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.3094141368293941</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.70307571152624</v>
+        <v>3.57125813246516</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.749328236855939</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.368934952061707</v>
+        <v>-5.50243656389063</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.601397831717509</v>
+        <v>1.54000238376888</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.3094141368293941</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.687502530602322</v>
+        <v>3.555684951541243</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.748515947292368</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.244454471337756</v>
+        <v>-5.377956083166678</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.650377734443519</v>
+        <v>1.58898228649489</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1030428437560276</v>
+        <v>-0.3094141368293941</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.686690241038752</v>
+        <v>3.554872661977672</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.758384726417441</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.254839666227645</v>
+        <v>-5.388341278056568</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.656092435612635</v>
+        <v>1.594696987664006</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1134280386459169</v>
+        <v>-0.3197993317192834</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.690327903229891</v>
+        <v>3.558510324168811</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120423</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.829221732193866</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.164085190199003</v>
+        <v>-5.297586802027926</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.763231231800517</v>
+        <v>1.701835783851888</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.2290448556906417</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.815617594623501</v>
+        <v>3.683800015562421</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881693</v>
+        <v>3.856479657110114</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.826090743012164</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.022368442384598</v>
+        <v>-5.155870054213521</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.816786941744578</v>
+        <v>1.755391493795949</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.2290448556906417</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.8124866054418</v>
+        <v>3.68066902638072</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.793075500228949</v>
+        <v>3.492100480842838</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.815241167004015</v>
+        <v>3.60480747375536</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.022368442384598</v>
+        <v>-5.155870054213521</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.816786941744578</v>
+        <v>1.755391493795949</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.02267356261727516</v>
+        <v>-0.2290448556906417</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.808304963990383</v>
+        <v>3.597871270741728</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>68.6%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>31.0%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>60.4%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.5%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.5%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-677.2%</t>
+          <t>-700.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24837.7%</t>
+          <t>-24638.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.7%</t>
+          <t>-208.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-267.4%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.1%</t>
+          <t>-132.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-246.9%</t>
+          <t>-232.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-160.8%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.2%</t>
+          <t>-68.1%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045691</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43785,10 +43785,10 @@
         <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.668418790368211</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.119052324986328</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43808,10 +43808,10 @@
         <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.668418790368211</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.119541463712203</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43831,10 +43831,10 @@
         <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.531973900140798</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.041754512197421</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43854,10 +43854,10 @@
         <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.531973900140798</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.076695596694964</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43877,10 +43877,10 @@
         <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.587618356407115</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.108659710640092</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43900,10 +43900,10 @@
         <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.933089671438995</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43923,10 +43923,10 @@
         <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.934107280569465</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43946,10 +43946,10 @@
         <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.924735312557221</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43969,10 +43969,10 @@
         <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.357459895105195</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.931039382556141</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -43992,10 +43992,10 @@
         <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.357459895105195</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.935804699389843</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44015,10 +44015,10 @@
         <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.368849131759997</v>
+        <v>1.405815606229521</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940463037501964</v>
+        <v>3.962642922183679</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44038,10 +44038,10 @@
         <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9510951082131597</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.687737514878926</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44061,10 +44061,10 @@
         <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.702052808321955</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44084,10 +44084,10 @@
         <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.70694495287588</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44107,10 +44107,10 @@
         <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9129984917923695</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.664719362517286</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44130,10 +44130,10 @@
         <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5469297646477168</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.438162425536944</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44153,10 +44153,10 @@
         <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3384389831960324</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.333406246404702</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44176,10 +44176,10 @@
         <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3585923366948448</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.353597008912558</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44199,10 +44199,10 @@
         <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1337926913292519</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.059272384141832</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44222,10 +44222,10 @@
         <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1337926913292519</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.057814922954695</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44245,10 +44245,10 @@
         <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.09752997149878867</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.081341678307589</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44268,10 +44268,10 @@
         <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3040417483858102</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.953540670831634</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44291,10 +44291,10 @@
         <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3040417483858102</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.955313597531894</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44314,10 +44314,10 @@
         <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4404592448270772</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.859795987134538</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44337,10 +44337,10 @@
         <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.434122977597822</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.851882522474182</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5020539630867268</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.809704522836804</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4216084539930649</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.864459388527242</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7179192382920774</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.685927432953667</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.439535710660019</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.434721143131479</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.432715193740357</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.3558145575154041</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.442973884409036</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>0.2146107148038916</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.439073449554731</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.1937345079619548</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.437478369609732</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.07884894716708413</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.195251151206634</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.400011464098613</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.0001347593089597865</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.195251151206634</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.395985159564209</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.1531678975096762</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.195251151206634</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.395883058242625</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.1523909596188013</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.199737596408023</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.395762707093223</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-0.2908527853223521</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.199737596408023</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.401113010391272</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-0.3030763907468632</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.250086659862245</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.378819592275917</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.3390823510936527</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.347705937283642</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.323289776444848</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44728,10 +44728,10 @@
         <v>-0.3578173945754242</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.401777436792001</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.293740433061404</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.943751556884919</v>
+        <v>-8.934927838825567</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4375369548124679</v>
+        <v>-0.4340074675887271</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.568132080654555</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.199440843862514</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.977404395393393</v>
+        <v>-8.968580677334041</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4465155357314212</v>
+        <v>-0.4429860485076804</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.668545448571592</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.143675377596728</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.903934563725944</v>
+        <v>-8.895110845666592</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4017559015710206</v>
+        <v>-0.3982264143472798</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.595075616904144</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.203128978090618</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.079058981112487</v>
+        <v>-9.070235263053135</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4572504477781214</v>
+        <v>-0.4537209605543806</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.770200034290688</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.112609548406208</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.313511075126977</v>
+        <v>-9.304687357067625</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.558250450285513</v>
+        <v>-0.5547209630617722</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.770200034290688</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.105390383504613</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.417885806153423</v>
+        <v>-9.409062088094071</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6066725334700678</v>
+        <v>-0.603143046246327</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.874574765317133</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.036093354114769</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.47067196175375</v>
+        <v>-9.461848243694398</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6266712058716424</v>
+        <v>-0.6231417186479016</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.970250251899531</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.979803852003887</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.596708755122039</v>
+        <v>-9.587885037062687</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6743921945898435</v>
+        <v>-0.6708627073661027</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.944998629089788</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.997648554318847</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.539636983226108</v>
+        <v>-9.530813265166756</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6475731501450701</v>
+        <v>-0.6440436629213293</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.944998629089788</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.001638890005248</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.681308824950229</v>
+        <v>-9.672485106890877</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7057171137334599</v>
+        <v>-0.7021876265097191</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.944998629089788</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.000163663106506</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.631717980525394</v>
+        <v>-9.622894262466042</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6708273657986541</v>
+        <v>-0.6672978785749133</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.895407784664954</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.044971579926279</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.482799646053538</v>
+        <v>-9.473975927994186</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6243111656565943</v>
+        <v>-0.6207816784328535</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.864158193929781</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.0506702007207</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.256954493334128</v>
+        <v>-9.248130775274774</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5243940315326214</v>
+        <v>-0.5208645443088802</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.822231518342618</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.085405279109207</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.132375836996536</v>
+        <v>-9.123552118937182</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4734234244415259</v>
+        <v>-0.4698939372177846</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.822231518342618</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.086544423665265</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.185271125040822</v>
+        <v>-9.176447406981469</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4919477654971329</v>
+        <v>-0.4884182782733912</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.817276172254171</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.092151405480441</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.113137949752941</v>
+        <v>-9.104314231693587</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4573607911433442</v>
+        <v>-0.4538313039196025</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.817276172254171</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.097885109719077</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.041771557143294</v>
+        <v>-9.03294783908394</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4385514964933503</v>
+        <v>-0.4350220092696087</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.745909779644524</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.130967682891001</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.948312523158069</v>
+        <v>-8.939488805098716</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.411051364212168</v>
+        <v>-0.4075218769884263</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.745909779644524</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.121084201578094</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.937659341604638</v>
+        <v>-8.928835623545284</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4086246520901691</v>
+        <v>-0.4050951648664278</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.745909779644524</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.11924964107872</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.839752302928147</v>
+        <v>-8.830928584868794</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3697621515930338</v>
+        <v>-0.3662326643692921</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.677924029783967</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.159740776021593</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.815798761952189</v>
+        <v>-8.806975043892836</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3595122290571569</v>
+        <v>-0.3559827418334156</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.65397048880801</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.174781406752661</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.551738823629393</v>
+        <v>-8.542915105570039</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2671485698897902</v>
+        <v>-0.2636190826660489</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.389910550485213</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.319957053584586</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.844659200124554</v>
+        <v>-7.835835482065201</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01289624585184423</v>
+        <v>0.01642573307558548</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.389910550485213</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.317170019924285</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.804474901758364</v>
+        <v>-7.79565118369901</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.02931358908616177</v>
+        <v>0.03284307630990302</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.349726252119023</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.341624222831841</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.641075030819001</v>
+        <v>-7.632251312759648</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09404035868266369</v>
+        <v>0.09756984590640494</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.18632638117966</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.439030966616216</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.407593808589403</v>
+        <v>-7.398770090530049</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1953572764123552</v>
+        <v>0.1988867636360969</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9528451589500615</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.587044128791827</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.257927417581888</v>
+        <v>-7.249103699522534</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2523316225024024</v>
+        <v>0.2558611097261436</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8599416677075256</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.63989401322439</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.125651943951001</v>
+        <v>-7.116828225891648</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3006092987017839</v>
+        <v>0.3041387859255251</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7276661940766389</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.714626784149949</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.969913611391259</v>
+        <v>-6.961089893331906</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3657196924133173</v>
+        <v>0.3692491796370589</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5719278615168973</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.81088484437343</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.720913812707678</v>
+        <v>-6.712090094648325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4782259531104085</v>
+        <v>0.4817554403341497</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3229280628333167</v>
+        <v>-0.2472458891152278</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.973191064807237</v>
+        <v>3.018600369038091</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.826503802480783</v>
+        <v>-6.817680084421429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3080140276019478</v>
+        <v>0.3115435148256895</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.428518052606421</v>
+        <v>-0.3528358788883322</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.781861141344156</v>
+        <v>2.827270445575009</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.84523870459938</v>
+        <v>-6.836414986540026</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3490644086315955</v>
+        <v>0.3525938958553372</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4341140622665523</v>
+        <v>-0.3584318885484635</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.827047877425164</v>
+        <v>2.872457181656017</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.697298663191781</v>
+        <v>-6.688474945132427</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2883615025064676</v>
+        <v>0.2918909897302093</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4137931463579947</v>
+        <v>-0.3381109726399059</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.719361504282131</v>
+        <v>2.764770808512984</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.644329140937792</v>
+        <v>-6.635505422878438</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3008353251545848</v>
+        <v>0.3043648123783265</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3608236241040059</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.742429231381046</v>
+        <v>2.787838535611899</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.600780734167102</v>
+        <v>-6.591957016107748</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3112940757677678</v>
+        <v>0.3148235629915095</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3608236241040059</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.735468619285953</v>
+        <v>2.780877923516806</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.567417527688333</v>
+        <v>-6.558593809628979</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3391017127404186</v>
+        <v>0.3426311999641598</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3608236241040059</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.749930973667096</v>
+        <v>2.795340277897949</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.459158390565811</v>
+        <v>-6.450334672506457</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3769374880486223</v>
+        <v>0.3804669752723635</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3608236241040059</v>
+        <v>-0.285141450385917</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.744463094126291</v>
+        <v>2.789872398357144</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.33586725574868</v>
+        <v>-6.327043537689327</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4237520359860514</v>
+        <v>0.4272815232097931</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2375324892868754</v>
+        <v>-0.1618503155687865</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.815935869027146</v>
+        <v>2.861345173257999</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.314718056845237</v>
+        <v>-6.305894338785883</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4399126937847537</v>
+        <v>0.4434421810084954</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.216383290383432</v>
+        <v>-0.1407011166653432</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.836326366606537</v>
+        <v>2.88173567083739</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.070952614861793</v>
+        <v>-6.062128896802439</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5331995789251822</v>
+        <v>0.5367290661489239</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.216383290383432</v>
+        <v>-0.1407011166653432</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.832107074953588</v>
+        <v>2.877516379184441</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.969189794584498</v>
+        <v>-5.960366076525144</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5760290209561165</v>
+        <v>0.5795585081798578</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.2031642219910033</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.842162829909061</v>
+        <v>2.887572134139914</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.719339400635423</v>
+        <v>-5.710515682576069</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6687112535194482</v>
+        <v>0.6722407407431898</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.2031642219910033</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.834904904892763</v>
+        <v>2.880314209123616</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.543447308167991</v>
+        <v>-5.534623590108637</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7426672140270698</v>
+        <v>0.7461967012508115</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.2031642219910033</v>
+        <v>-0.1274820482729145</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.838504028413412</v>
+        <v>2.883913332644265</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.372000845145528</v>
+        <v>-5.363177127086174</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8245733052906088</v>
+        <v>0.8281027925143505</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.03171775896854018</v>
+        <v>0.04396441474954865</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.954699412281443</v>
+        <v>3.000108716512297</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.297711279407189</v>
+        <v>-5.288887561347835</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8533096092022414</v>
+        <v>0.8568390964259831</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.0425718067697991</v>
+        <v>0.1182539804878879</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.998293629340744</v>
+        <v>3.043702933571597</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.234075537173254</v>
+        <v>-5.2252518191139</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8834587071501327</v>
+        <v>0.886988194373874</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1062075490037336</v>
+        <v>0.1818897227218225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.041169875735422</v>
+        <v>3.086579179966275</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.122648777847334</v>
+        <v>-5.11382505978798</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9092236696642964</v>
+        <v>0.912753156888038</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1062075490037336</v>
+        <v>0.1818897227218225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.022364134519218</v>
+        <v>3.067773438750071</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.133151400912623</v>
+        <v>-5.124327682853269</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.906765697063058</v>
+        <v>0.9102951842867997</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.09570492593844476</v>
+        <v>0.1713870996565336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.017805637304922</v>
+        <v>3.063214941535775</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.060908832741428</v>
+        <v>-5.052085114682074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9395920381663561</v>
+        <v>0.9431215253900977</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.09570492593844476</v>
+        <v>0.1713870996565336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.021734951139742</v>
+        <v>3.067144255370595</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.043195145863563</v>
+        <v>-5.034371427804209</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9473560968348425</v>
+        <v>0.9508855840585837</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.09888625483536156</v>
+        <v>0.1745684285534504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.024322332395232</v>
+        <v>3.069731636626085</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.934390260383836</v>
+        <v>-4.925566542324482</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9878761222467267</v>
+        <v>0.9914056094704682</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.09888625483536156</v>
+        <v>0.1745684285534504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.021320403615225</v>
+        <v>3.066729707846079</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.714369462346825</v>
+        <v>-4.705545744287472</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077463478472145</v>
+        <v>1.080992965695887</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2401060999033418</v>
+        <v>0.3157882736214306</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.107631347666628</v>
+        <v>3.153040651897481</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.581501773283548</v>
+        <v>-4.572678055224194</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146504736899279</v>
+        <v>1.150034224123021</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2401060999033418</v>
+        <v>0.3157882736214306</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.123525530468451</v>
+        <v>3.168934834699304</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.461328689919049</v>
+        <v>-4.452504971859695</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.195719814685381</v>
+        <v>1.199249301909122</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3602791832678408</v>
+        <v>0.4359613569859296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.196775224927452</v>
+        <v>3.242184529158306</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.316656544819311</v>
+        <v>-4.307832826759958</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.263676775286716</v>
+        <v>1.267206262510457</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5049513283675782</v>
+        <v>0.580633502085667</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.293666614548735</v>
+        <v>3.339075918779588</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.376531372177004</v>
+        <v>-4.36770765411765</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.225764335745064</v>
+        <v>1.229293822968806</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.445076501009886</v>
+        <v>0.5207586747279749</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.243779209535545</v>
+        <v>3.289188513766399</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.256711141266167</v>
+        <v>-4.247887423206813</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.288981597343608</v>
+        <v>1.292511084567349</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.445076501009886</v>
+        <v>0.5207586747279749</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.259068378769754</v>
+        <v>3.304477683000607</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.259180847727973</v>
+        <v>-4.250357129668619</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.195637914081327</v>
+        <v>1.199167401305068</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4426067945480799</v>
+        <v>0.5182889682661687</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.165230754215111</v>
+        <v>3.210640058445965</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.327551034051983</v>
+        <v>-4.318727315992629</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.087551701037024</v>
+        <v>1.091081188260766</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4518824935842948</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.090058035122142</v>
+        <v>3.135467339352995</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.34133908689903</v>
+        <v>-4.332515368839676</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.072473188530097</v>
+        <v>1.076002675753838</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4518824935842948</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.080494743754033</v>
+        <v>3.125904047984887</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.396859162791619</v>
+        <v>-4.388035444732266</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.187295994865263</v>
+        <v>1.190825482089005</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4518824935842948</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.217525580446236</v>
+        <v>3.262934884677089</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.22138490299915</v>
+        <v>-4.212561184939796</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.262052930774039</v>
+        <v>1.265582417997781</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4518824935842948</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.222092812438023</v>
+        <v>3.267502116668877</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.332321155640399</v>
+        <v>-4.323497437581045</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.193420458478747</v>
+        <v>1.196949945702488</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4518824935842948</v>
+        <v>0.5275646673023836</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.197834841199231</v>
+        <v>3.243244145430084</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.298657610168116</v>
+        <v>-4.289833892108763</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.135424190069109</v>
+        <v>1.138953677292851</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4855460390565767</v>
+        <v>0.5612282127746655</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.146571281884049</v>
+        <v>3.191980586114902</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.238804990964393</v>
+        <v>-4.229981272905039</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.169537624182731</v>
+        <v>1.173067111406472</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4855460390565767</v>
+        <v>0.5612282127746655</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.156743668316182</v>
+        <v>3.202152972547035</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.152561527938015</v>
+        <v>-4.143737809878662</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.198981279967142</v>
+        <v>1.202510767190884</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4855460390565767</v>
+        <v>0.5612282127746655</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.151689938890042</v>
+        <v>3.197099243120896</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.197868347336995</v>
+        <v>-4.189044629277642</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.172634327652076</v>
+        <v>1.176163814875817</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4447358760473459</v>
+        <v>0.5204180497654347</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.118979616529029</v>
+        <v>3.164388920759882</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.226901452039296</v>
+        <v>-4.218077733979943</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.161572958804257</v>
+        <v>1.165102446027999</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4447358760473459</v>
+        <v>0.5204180497654347</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.119531489562131</v>
+        <v>3.164940793792984</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.134090970588437</v>
+        <v>-4.125267252529083</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.127969843275967</v>
+        <v>1.131499330499708</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5375463574982052</v>
+        <v>0.6132285312162941</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.104490470324012</v>
+        <v>3.149899774554865</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.178480439917864</v>
+        <v>-4.169656721858511</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.112087531468796</v>
+        <v>1.115617018692538</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4931568881687776</v>
+        <v>0.5688390618868664</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.079730264650956</v>
+        <v>3.12513956888181</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.295022045023207</v>
+        <v>-4.286198326963853</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.060546597938382</v>
+        <v>1.064076085162124</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3766152830634348</v>
+        <v>0.4522974567815236</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.004881010099473</v>
+        <v>3.050290314330327</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.182645043840534</v>
+        <v>-4.403116273601231</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.110988694242119</v>
+        <v>1.02280020233784</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3766152830634348</v>
+        <v>0.4522974567815236</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.010372305930141</v>
+        <v>3.055781610160994</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.210425441741886</v>
+        <v>-4.430896671502584</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.111373736850117</v>
+        <v>1.023185244945838</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3488348851620817</v>
+        <v>0.4245170588801706</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.005201268957868</v>
+        <v>3.050610573188721</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.328806114472025</v>
+        <v>-4.549277344232722</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9023771877587148</v>
+        <v>0.8141886958544358</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2816170330111055</v>
+        <v>0.3572992067291944</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.803226277667935</v>
+        <v>2.848635581898789</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.437420192915356</v>
+        <v>-4.657891422676053</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9790812171005878</v>
+        <v>0.8908927251963088</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2816170330111055</v>
+        <v>0.3572992067291944</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.923375938387141</v>
+        <v>2.968785242617995</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.402011154667213</v>
+        <v>-4.622482384427911</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.007757858502168</v>
+        <v>0.919569366597889</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2816170330111055</v>
+        <v>0.3572992067291944</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.937888964489464</v>
+        <v>2.983298268720318</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.363627492109062</v>
+        <v>-4.58409872186976</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.020530764867797</v>
+        <v>0.9323422729635182</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3200006955692567</v>
+        <v>0.3956828692873455</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.958338603366724</v>
+        <v>3.003747907597577</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.186511162073896</v>
+        <v>-4.406982391834593</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.088106325727165</v>
+        <v>0.9999178338228865</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3200006955692567</v>
+        <v>0.3956828692873455</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.955067632212026</v>
+        <v>3.000476936442879</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.231603406907442</v>
+        <v>-4.452074636668139</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.07075281955566</v>
+        <v>0.9825643276513814</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2581046523998669</v>
+        <v>0.3337868261179557</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.918613398072305</v>
+        <v>2.964022702303158</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.052227985668674</v>
+        <v>-4.272699215429371</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.136289963357582</v>
+        <v>1.048101471453303</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4148814105705856</v>
+        <v>0.4905635842886744</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.00646642828115</v>
+        <v>3.051875732512003</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.09724219918928</v>
+        <v>-4.317713428949977</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.099091733280929</v>
+        <v>1.01090324137665</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.384532515255981</v>
+        <v>0.4602146889740698</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.969064546423977</v>
+        <v>3.01447385065483</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.364246709461715</v>
+        <v>-4.584717939222412</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9979814915109009</v>
+        <v>0.9097929996066219</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1901694772130324</v>
+        <v>0.2658516509311212</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.858138285937154</v>
+        <v>2.903547590168007</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.465444490898888</v>
+        <v>-4.685915720659585</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9567063008325332</v>
+        <v>0.8685178089282544</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1217606636677132</v>
+        <v>0.197442837385802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.816296919706464</v>
+        <v>2.861706223937317</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.458933524284575</v>
+        <v>-4.679404754045272</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9569106490325749</v>
+        <v>0.8687221571282961</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1217606636677132</v>
+        <v>0.197442837385802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.813896881260781</v>
+        <v>2.859306185491634</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.439895396577278</v>
+        <v>-4.660366626337975</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9610506193237389</v>
+        <v>0.8728621274194599</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.06357705233651867</v>
+        <v>0.1392592260546075</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.775511433670309</v>
+        <v>2.820920737901162</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.471022027727896</v>
+        <v>-4.691493257488593</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.067894368497682</v>
+        <v>0.9797058765934028</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.06357705233651867</v>
+        <v>0.1392592260546075</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.894805835304499</v>
+        <v>2.940215139535352</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.484888789061814</v>
+        <v>-4.83669747342073</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.063180992950248</v>
+        <v>0.9224575192066817</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.02571913560269573</v>
+        <v>0.09587756060435393</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.872924414250339</v>
+        <v>2.915019469251334</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.440084617521884</v>
+        <v>-4.7918933018808</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.087111191963146</v>
+        <v>0.9463877182195797</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.02571913560269573</v>
+        <v>0.09587756060435393</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.878932944647265</v>
+        <v>2.92102799964826</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.292341647286881</v>
+        <v>-4.644150331645798</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.044158601334347</v>
+        <v>0.9034351275907802</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1935264928375789</v>
+        <v>0.2636849178392371</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.877567580265394</v>
+        <v>2.919662635266389</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.37616286856158</v>
+        <v>-4.727971552920496</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.013423734355948</v>
+        <v>0.8727002606123817</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1935264928375789</v>
+        <v>0.2636849178392371</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.880361201796875</v>
+        <v>2.92245625679787</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.370010162508795</v>
+        <v>-4.721818846867712</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.01654716516872</v>
+        <v>0.8758236914251538</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1996791988903632</v>
+        <v>0.2698376238920214</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.884715173820204</v>
+        <v>2.926810228821199</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.386819460659297</v>
+        <v>-4.738628145018214</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.00890392264863</v>
+        <v>0.8681804489050633</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1828699007398615</v>
+        <v>0.2530283257415197</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.873710071670013</v>
+        <v>2.915805126671008</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.324521461883175</v>
+        <v>-4.676330146242091</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.1001586759559</v>
+        <v>0.9594352022123331</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1828699007398615</v>
+        <v>0.2530283257415197</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.940045625466834</v>
+        <v>2.982140680467829</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.122731264218017</v>
+        <v>-4.474539948576933</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.98316675673609</v>
+        <v>0.8424432829925235</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3808880929090159</v>
+        <v>0.4510465179106741</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.861148542482454</v>
+        <v>2.903243597483449</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.173617976904212</v>
+        <v>-4.525426661263128</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.033102303983787</v>
+        <v>0.8923788302402207</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3300013802228214</v>
+        <v>0.4001598052244796</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.900906747192912</v>
+        <v>2.943001802193908</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.271358521529186</v>
+        <v>-4.623167205888103</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.008633822249841</v>
+        <v>0.8679103485062747</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3141121020898412</v>
+        <v>0.3842705270914994</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.906000916429168</v>
+        <v>2.948095971430163</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.331567819534471</v>
+        <v>-4.683376503893387</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9830860838723989</v>
+        <v>0.8423626101288324</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2539028040845567</v>
+        <v>0.3240612290862149</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.868411318450669</v>
+        <v>2.910506373451664</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.255145773102544</v>
+        <v>-4.606954457461461</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.012146520485098</v>
+        <v>0.8714230467415316</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2539028040845567</v>
+        <v>0.3240612290862149</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.866902936490598</v>
+        <v>2.908997991491592</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.210772641463976</v>
+        <v>-4.562581325822892</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.029758640575962</v>
+        <v>0.8890351668323953</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.2982759357231253</v>
+        <v>0.3684343607247835</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.893389682909175</v>
+        <v>2.93548473791017</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.233252992322861</v>
+        <v>-4.585061676681777</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.015160294370998</v>
+        <v>0.8744368206274318</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.2982759357231253</v>
+        <v>0.3684343607247835</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.887783477047766</v>
+        <v>2.92987853204876</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.185597261761805</v>
+        <v>-4.537405946120721</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.040604343623225</v>
+        <v>0.8998808698796588</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3459316662841809</v>
+        <v>0.4160900912858391</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.922758672412203</v>
+        <v>2.964853727413198</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.08507910326305</v>
+        <v>-4.436887787621966</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.085703980397452</v>
+        <v>0.9449805066538854</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4464498247829355</v>
+        <v>0.5166082497845936</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.987961940886181</v>
+        <v>3.030056995887176</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.14574569366544</v>
+        <v>-4.497554378024356</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.048192016712368</v>
+        <v>0.9074685429688019</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3647515080644018</v>
+        <v>0.43490993306606</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.925697623330933</v>
+        <v>2.967792678331928</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.100907292057041</v>
+        <v>-4.452715976415957</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.070225079966356</v>
+        <v>0.9295016062227899</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3692949410092713</v>
+        <v>0.4394533660109294</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.932521385708483</v>
+        <v>2.974616440709478</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917052</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.120405748299049</v>
+        <v>-4.472214432657966</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.066586637100631</v>
+        <v>0.9258631633570646</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.321210299729367</v>
+        <v>0.3913687247310251</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.907831540571618</v>
+        <v>2.949926595572613</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.076202911213149</v>
+        <v>-4.428011595572065</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.090147374462829</v>
+        <v>0.949423900719262</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3654131368152674</v>
+        <v>0.4355715618169256</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.940232845350996</v>
+        <v>2.982327900351991</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.113181938876592</v>
+        <v>-4.464990623235508</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.073765763866699</v>
+        <v>0.9330422901231323</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.402387038606598</v>
+        <v>0.4725454636082561</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.960827186895042</v>
+        <v>3.002922241896037</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.954890521337319</v>
+        <v>-4.306699205696236</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.188330096065447</v>
+        <v>1.047606622321881</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.402387038606598</v>
+        <v>0.4725454636082561</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.012074952078081</v>
+        <v>3.054170007079076</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.747248517702843</v>
+        <v>-4.099057202061759</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.269827602113491</v>
+        <v>1.129104128369925</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6100290422410741</v>
+        <v>0.6801874672427323</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.13510085885302</v>
+        <v>3.177195913854015</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.696216424980315</v>
+        <v>-4.048025109339232</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.285188667440772</v>
+        <v>1.144465193697206</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6610611349636021</v>
+        <v>0.7312195599652602</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.160668342724807</v>
+        <v>3.202763397725802</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.630992243853109</v>
+        <v>-3.982800928212026</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.328465743984359</v>
+        <v>1.187742270240793</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7262853160908077</v>
+        <v>0.7964437410924659</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.216990255493835</v>
+        <v>3.259085310494831</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.593565223781976</v>
+        <v>-3.945373908140893</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.339397524312093</v>
+        <v>1.198674050568526</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7315368541199894</v>
+        <v>0.8016952791216475</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.216102150610625</v>
+        <v>3.25819720561162</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.613676879816684</v>
+        <v>-3.965485564175601</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.33260965422945</v>
+        <v>1.191886180485884</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.7425641991174086</v>
+        <v>0.8127226241190667</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.223975349940317</v>
+        <v>3.266070404941312</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.559932065389479</v>
+        <v>-3.911740749748396</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.514665351021543</v>
+        <v>1.373941877277976</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.7526275085578705</v>
+        <v>0.8227859335595287</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.390571106625805</v>
+        <v>3.432666161626799</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.485149804364466</v>
+        <v>-3.836958488723384</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.664691164649365</v>
+        <v>1.523967690905798</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8274097695828831</v>
+        <v>0.8975681945845413</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.555553372458629</v>
+        <v>3.597648427459624</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.459065720100658</v>
+        <v>-3.810874404459576</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.666832774368747</v>
+        <v>1.526109300625181</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8274097695828831</v>
+        <v>0.8975681945845413</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.547261348472488</v>
+        <v>3.589356403473483</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.380934539251712</v>
+        <v>-3.732743223610629</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.696278442292106</v>
+        <v>1.555554968548539</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9015865804665677</v>
+        <v>0.9717450054682258</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.589960630586479</v>
+        <v>3.632055685587473</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.372042077858429</v>
+        <v>-3.723850762217346</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.71738983257621</v>
+        <v>1.576666358832643</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9015865804665677</v>
+        <v>0.9717450054682258</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.60751503631327</v>
+        <v>3.649610091314265</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.540518194828306</v>
+        <v>-3.892326879187224</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.641854433192843</v>
+        <v>1.501130959449276</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8736387447499869</v>
+        <v>0.9437971697516451</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.582601382287905</v>
+        <v>3.6246964372889</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.842718665966723</v>
+        <v>-3.19452735032564</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.902243941925338</v>
+        <v>1.761520468181771</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8032906853795763</v>
+        <v>0.8734491103812343</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.521662243853521</v>
+        <v>3.563757298854516</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.819997562283571</v>
+        <v>-3.171806246642488</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.901996405895504</v>
+        <v>1.761272932151937</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8032906853795763</v>
+        <v>0.8734491103812343</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.512326266350425</v>
+        <v>3.55442132135142</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.949199375577613</v>
+        <v>-3.30100805993653</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.009221806429056</v>
+        <v>1.868498332685489</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.674088872085534</v>
+        <v>0.7442472970871921</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.593711304225169</v>
+        <v>3.635806359226164</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.103980382355869</v>
+        <v>-3.455789066714786</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.9843872262114</v>
+        <v>1.843663752467833</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6407211980310579</v>
+        <v>0.7108796230327159</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.61076852228613</v>
+        <v>3.652863577287125</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799966</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.096925692140695</v>
+        <v>-3.448734376499612</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.983884458287015</v>
+        <v>1.843160984543448</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6477758882462317</v>
+        <v>0.7179343132478897</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.611676692404779</v>
+        <v>3.653771747405774</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.069974467814207</v>
+        <v>-3.421783152173124</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.004671101662352</v>
+        <v>1.863947627918785</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6626562342739508</v>
+        <v>0.7328146592756088</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.630611053666152</v>
+        <v>3.672706108667147</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.205927475870523</v>
+        <v>-3.557736160229441</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.134393030584785</v>
+        <v>1.993669556841218</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6626562342739508</v>
+        <v>0.7328146592756088</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.814714185811112</v>
+        <v>3.856809240812107</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714428</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.228335593675395</v>
+        <v>-3.580144278034313</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.117546478365829</v>
+        <v>1.976823004622262</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6626562342739508</v>
+        <v>0.7328146592756088</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.806830880714105</v>
+        <v>3.8489259357151</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.376341361154795</v>
+        <v>-3.728150045513712</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.060398170923706</v>
+        <v>1.91967469718014</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.5759292254104094</v>
+        <v>0.6460876504120674</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.756848674945618</v>
+        <v>3.798943729946612</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.385782287043325</v>
+        <v>-3.913137467117562</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.112875518290142</v>
+        <v>1.901933446260447</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.6983563429538008</v>
+        <v>0.5933901999840563</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.8865586631935</v>
+        <v>3.823578977411653</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.438055894378966</v>
+        <v>-3.965411074453204</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.094857169901186</v>
+        <v>1.883915097871491</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.6460827356181595</v>
+        <v>0.5411165926484151</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.858085593337416</v>
+        <v>3.795105907555569</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.514385871979872</v>
+        <v>-4.041741052054109</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.062436991754599</v>
+        <v>1.851494919724904</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.6460827356181595</v>
+        <v>0.5411165926484151</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.856197406231191</v>
+        <v>3.793217720449344</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.716639592304225</v>
+        <v>-4.243994772378463</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.97635573322772</v>
+        <v>1.765413661198025</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.4438290152938061</v>
+        <v>0.3388628723240616</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.729665403639441</v>
+        <v>3.666685717857595</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.878208017831481</v>
+        <v>-4.405563197905718</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.91016237322697</v>
+        <v>1.699220301197275</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3170460914959267</v>
+        <v>0.2120799485261822</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.652029659570866</v>
+        <v>3.589049973789019</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754911907647108</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.010509309929034</v>
+        <v>-4.537864490003272</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.870315263253867</v>
+        <v>1.659373191224172</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3170460914959267</v>
+        <v>0.2120799485261822</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.665103066436785</v>
+        <v>3.602123380654938</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749896851763536</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.184878598397765</v>
+        <v>-4.539426132818131</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.792572744649315</v>
+        <v>1.658748534098229</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1863569721406489</v>
+        <v>0.2120799485261822</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.578694791606558</v>
+        <v>3.602123380654938</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.212779385507238</v>
+        <v>-4.567326919927604</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.779936470932528</v>
+        <v>1.646112260381442</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.1517600479977141</v>
+        <v>0.1774830243832474</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.556460678247799</v>
+        <v>3.579889267296179</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.68490993917253</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.335305488210132</v>
+        <v>-4.689853022630498</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.727690473828569</v>
+        <v>1.593866263277483</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.02923394529482021</v>
+        <v>0.05495692168035354</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.479709460603261</v>
+        <v>3.503138049651642</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.565819984395721</v>
+        <v>-4.920367518816087</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.702190634944837</v>
+        <v>1.568366424393751</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.2012805508907685</v>
+        <v>-0.1755575745052352</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.408106722482412</v>
+        <v>3.431535311530792</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814661</v>
+        <v>3.640764248199808</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.822540802390545</v>
+        <v>-5.177088336810911</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.739814026748755</v>
+        <v>1.605989816197668</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.3096951250345834</v>
+        <v>-0.28397214864905</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.48336969699797</v>
+        <v>3.50679828604635</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.976527220166686</v>
+        <v>-5.331074754587052</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.747199728783938</v>
+        <v>1.613375518232852</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.3096951250345834</v>
+        <v>-0.28397214864905</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.55234996614361</v>
+        <v>3.57577855519199</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.61993717680853</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.92600531633902</v>
+        <v>-5.280552850759386</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.753459692435125</v>
+        <v>1.619635481884039</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.3096951250345834</v>
+        <v>-0.28397214864905</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.538401168263731</v>
+        <v>3.561829757312111</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.178480470346744</v>
+        <v>-5.53302800476711</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.664340119887449</v>
+        <v>1.530515909336363</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.3096951250345834</v>
+        <v>-0.28397214864905</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.550271657319145</v>
+        <v>3.573700246367525</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.6740426963583</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.447953272268452</v>
+        <v>-5.802500806688818</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.55776153363771</v>
+        <v>1.423937323086624</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.3096951250345834</v>
+        <v>-0.28397214864905</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.551482191838089</v>
+        <v>3.574910780886468</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663523617637089</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.605497343997894</v>
+        <v>-5.96004487841826</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.498865647173255</v>
+        <v>1.365041436622168</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.3765969301748578</v>
+        <v>-0.3508739537893245</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.515462850981245</v>
+        <v>3.538891440029625</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652163313301345</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.883461739581167</v>
+        <v>-6.238009274001533</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.382757741676135</v>
+        <v>1.248933531125048</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.4662166644603421</v>
+        <v>-0.4404936880748088</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.456768863146144</v>
+        <v>3.480197452194524</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667976467215472</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.000429432220058</v>
+        <v>-6.354976966640424</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.498174721319623</v>
+        <v>1.364350510768536</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.4662166644603421</v>
+        <v>-0.4404936880748088</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.618972919845188</v>
+        <v>3.642401508893568</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696553628456694</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.085147374441012</v>
+        <v>-6.439694908861378</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.459134182395055</v>
+        <v>1.325309971843969</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.5513326933883884</v>
+        <v>-0.5256097170028551</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.562749940452175</v>
+        <v>3.586178529500555</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750058176253289</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.167082192709895</v>
+        <v>-6.521629727130261</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.436589672655993</v>
+        <v>1.302765462104907</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.5612674389754686</v>
+        <v>-0.5355444625899353</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.567018510668418</v>
+        <v>3.590447099716798</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332687</v>
+        <v>3.783647027717834</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.269058314958302</v>
+        <v>-6.623605849378668</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.404724862212533</v>
+        <v>1.270900651661446</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.6632435612238762</v>
+        <v>-0.6375205848383428</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.514758475775276</v>
+        <v>3.538187064823656</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798310944616951</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.159052031481081</v>
+        <v>-6.513599565901447</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.440880262847597</v>
+        <v>1.30705605229651</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.640038989306601</v>
+        <v>-0.6143160129210676</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.520834106169816</v>
+        <v>3.544262695218196</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785578085203666</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.015992455740156</v>
+        <v>-6.370539990160522</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.502354103865941</v>
+        <v>1.368529893314855</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.6320255627166217</v>
+        <v>-0.6063025863310884</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.529892172845778</v>
+        <v>3.553320761894158</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777251572436931</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.714545730268318</v>
+        <v>-6.069093264688684</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.630193676937212</v>
+        <v>1.496369466386126</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.3305788372447844</v>
+        <v>-0.3048558608592511</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.718021091011416</v>
+        <v>3.741449680059796</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812650101064768</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.739135974503502</v>
+        <v>-6.093683508923868</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.621328756995849</v>
+        <v>1.487504546444762</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.3305788372447844</v>
+        <v>-0.3048558608592511</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.718992268764127</v>
+        <v>3.742420857812506</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821198342859302</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.688097598496982</v>
+        <v>-6.042645132917348</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.642587011778212</v>
+        <v>1.508762801227126</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.3305788372447844</v>
+        <v>-0.3048558608592511</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.719835173143882</v>
+        <v>3.743263762192262</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831748677354685</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.646958303630351</v>
+        <v>-6.001505838050717</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.67808082859901</v>
+        <v>1.544256618047924</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.2894395423781536</v>
+        <v>-0.2637165659926203</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.763556848938006</v>
+        <v>3.786985437986386</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825767093085621</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.536352163550749</v>
+        <v>-5.890899697971115</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.538507280754786</v>
+        <v>1.404683070203699</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.1788334022985516</v>
+        <v>-0.1531104259130183</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.646104529109702</v>
+        <v>3.669533118158082</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804703121462783</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.666932898081591</v>
+        <v>-6.021480432501957</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.489777031016412</v>
+        <v>1.355952820465326</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.3094141368293941</v>
+        <v>-0.2836911604438608</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.57125813246516</v>
+        <v>3.59468672151354</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.7750430212186</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.50243656389063</v>
+        <v>-5.856984098310996</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.54000238376888</v>
+        <v>1.406178173217793</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.3094141368293941</v>
+        <v>-0.2836911604438608</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.555684951541243</v>
+        <v>3.579113540589622</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821044820462771</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.377956083166678</v>
+        <v>-5.732503617587044</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.58898228649489</v>
+        <v>1.455158075943804</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.3094141368293941</v>
+        <v>-0.2836911604438608</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.554872661977672</v>
+        <v>3.578301251026052</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832321184533052</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.388341278056568</v>
+        <v>-5.742666578201193</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.594696987664006</v>
+        <v>1.460961670823216</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.3197993317192834</v>
+        <v>-0.2938541210580104</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.558510324168811</v>
+        <v>3.582072253782635</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834429654120425</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.297586802027926</v>
+        <v>-5.651912102172552</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.701835783851888</v>
+        <v>1.568100467011098</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.2290448556906417</v>
+        <v>-0.2030996450293687</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.683800015562421</v>
+        <v>3.707361945176245</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.856479657110114</v>
+        <v>3.855134695881701</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.155870054213521</v>
+        <v>-5.510195354358147</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.755391493795949</v>
+        <v>1.621656176955158</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.2290448556906417</v>
+        <v>-0.2030996450293687</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.68066902638072</v>
+        <v>3.704230955994543</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.492100480842838</v>
+        <v>3.807495453259816</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.60480747375536</v>
+        <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.155870054213521</v>
+        <v>-5.393054335571869</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.755391493795949</v>
+        <v>1.673043479409061</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.2290448556906417</v>
+        <v>-0.08595862624309109</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.597871270741728</v>
+        <v>3.779046462205701</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240729.xlsx
+++ b/tame_output/ON/bt/strategyON_20240729.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-700.9%</t>
+          <t>-667.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24638.9%</t>
+          <t>-24635.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-208.9%</t>
+          <t>-195.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.7%</t>
+          <t>-116.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.6%</t>
+          <t>-228.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-65.6%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706666</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.176447406981469</v>
+        <v>-9.174866254521683</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4884182782733912</v>
+        <v>-0.4877858172894776</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.739948427110283</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.138548052566774</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.104314231693587</v>
+        <v>-9.102733079233802</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4538313039196025</v>
+        <v>-0.4531988429356884</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.739948427110283</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.144281756805411</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.03294783908394</v>
+        <v>-9.031366686624155</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4350220092696087</v>
+        <v>-0.4343895482856945</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.668582034500635</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.177364329977334</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.939488805098716</v>
+        <v>-8.937907652638931</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4075218769884263</v>
+        <v>-0.4068894160045127</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.668582034500635</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.167480848664427</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.928835623545284</v>
+        <v>-8.927254471085499</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4050951648664278</v>
+        <v>-0.4044627038825137</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.668582034500635</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.165646288165053</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.830928584868794</v>
+        <v>-8.829347432409008</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3662326643692921</v>
+        <v>-0.365600203385378</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.600596284640079</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.206137423107926</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.806975043892836</v>
+        <v>-8.805393891433051</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3559827418334156</v>
+        <v>-0.3553502808495015</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.576642743664121</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.221178053838994</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.542915105570039</v>
+        <v>-8.541333953110254</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2636190826660489</v>
+        <v>-0.2629866216821348</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.312582805341325</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.36635370067092</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.835835482065201</v>
+        <v>-7.834254329605415</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01642573307558548</v>
+        <v>0.0170581940594996</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.312582805341325</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.363566667010619</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.79565118369901</v>
+        <v>-7.794070031239225</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.03284307630990302</v>
+        <v>0.03347553729381714</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.272398506975134</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.388020869918174</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.632251312759648</v>
+        <v>-7.630670160299863</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09756984590640494</v>
+        <v>0.09820230689031906</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.108998636035771</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.485427613702549</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.398770090530049</v>
+        <v>-7.397188938070264</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1988867636360969</v>
+        <v>0.199519224620011</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8755174138061728</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.633440775878161</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.249103699522534</v>
+        <v>-7.247522547062749</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2558611097261436</v>
+        <v>0.2564935707100577</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7826139225636368</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.686290660310723</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.116828225891648</v>
+        <v>-7.115247073431862</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3041387859255251</v>
+        <v>0.3047712469094392</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6503384489327502</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.761023431236282</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.961089893331906</v>
+        <v>-6.959508740872121</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3692491796370589</v>
+        <v>0.3698816406209726</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4946001163730086</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.857281491459764</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712090094648325</v>
+        <v>-6.71050894218854</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4817554403341497</v>
+        <v>0.4823879013180639</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2472458891152278</v>
+        <v>-0.2456003176894279</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.018600369038091</v>
+        <v>3.019587711893571</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.817680084421429</v>
+        <v>-6.816098931961644</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3115435148256895</v>
+        <v>0.3121759758096037</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3528358788883322</v>
+        <v>-0.3511903074625323</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.827270445575009</v>
+        <v>2.82825778843049</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.836414986540026</v>
+        <v>-6.834833834080241</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3525938958553372</v>
+        <v>0.3532263568392509</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3584318885484635</v>
+        <v>-0.3567863171226636</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.872457181656017</v>
+        <v>2.873444524511497</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.688474945132427</v>
+        <v>-6.686893792672642</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2918909897302093</v>
+        <v>0.292523450714123</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3381109726399059</v>
+        <v>-0.336465401214106</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.764770808512984</v>
+        <v>2.765758151368464</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.635505422878438</v>
+        <v>-6.633924270418653</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3043648123783265</v>
+        <v>0.3049972733622406</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2834958789601171</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.787838535611899</v>
+        <v>2.788825878467379</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.591957016107748</v>
+        <v>-6.590375863647963</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3148235629915095</v>
+        <v>0.3154560239754236</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2834958789601171</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.780877923516806</v>
+        <v>2.781865266372286</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.558593809628979</v>
+        <v>-6.557012657169194</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3426311999641598</v>
+        <v>0.3432636609480739</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2834958789601171</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.795340277897949</v>
+        <v>2.796327620753429</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.450334672506457</v>
+        <v>-6.448753520046672</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3804669752723635</v>
+        <v>0.3810994362562776</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.285141450385917</v>
+        <v>-0.2834958789601171</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.789872398357144</v>
+        <v>2.790859741212624</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.327043537689327</v>
+        <v>-6.325462385229542</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4272815232097931</v>
+        <v>0.4279139841937067</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1618503155687865</v>
+        <v>-0.1602047441429866</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.861345173257999</v>
+        <v>2.862332516113479</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.305894338785883</v>
+        <v>-6.304313186326098</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4434421810084954</v>
+        <v>0.4440746419924095</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.1390555452395433</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88173567083739</v>
+        <v>2.88272301369287</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.062128896802439</v>
+        <v>-6.060547744342654</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5367290661489239</v>
+        <v>0.537361527132838</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1407011166653432</v>
+        <v>-0.1390555452395433</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.877516379184441</v>
+        <v>2.878503722039921</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.960366076525144</v>
+        <v>-5.958784924065359</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5795585081798578</v>
+        <v>0.5801909691637719</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.1258364768471146</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.887572134139914</v>
+        <v>2.888559476995394</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.710515682576069</v>
+        <v>-5.708934530116284</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6722407407431898</v>
+        <v>0.672873201727104</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.1258364768471146</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.880314209123616</v>
+        <v>2.881301551979096</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.534623590108637</v>
+        <v>-5.533042437648852</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7461967012508115</v>
+        <v>0.7468291622347256</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1274820482729145</v>
+        <v>-0.1258364768471146</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.883913332644265</v>
+        <v>2.884900675499745</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.363177127086174</v>
+        <v>-5.361595974626389</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8281027925143505</v>
+        <v>0.8287352534982646</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04396441474954865</v>
+        <v>0.04560998617534856</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.000108716512297</v>
+        <v>3.001096059367777</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.288887561347835</v>
+        <v>-5.28730640888805</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8568390964259831</v>
+        <v>0.8574715574098972</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1182539804878879</v>
+        <v>0.1198995519136878</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.043702933571597</v>
+        <v>3.044690276427077</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.2252518191139</v>
+        <v>-5.223670666654115</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.886988194373874</v>
+        <v>0.8876206553577881</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.1835352941476224</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.086579179966275</v>
+        <v>3.087566522821755</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.11382505978798</v>
+        <v>-5.112243907328195</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.912753156888038</v>
+        <v>0.9133856178719517</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1818897227218225</v>
+        <v>0.1835352941476224</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.067773438750071</v>
+        <v>3.068760781605551</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.124327682853269</v>
+        <v>-5.122746530393484</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9102951842867997</v>
+        <v>0.9109276452707138</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1713870996565336</v>
+        <v>0.1730326710823335</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.063214941535775</v>
+        <v>3.064202284391255</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.052085114682074</v>
+        <v>-5.050503962222289</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9431215253900977</v>
+        <v>0.9437539863740119</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1713870996565336</v>
+        <v>0.1730326710823335</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.067144255370595</v>
+        <v>3.068131598226075</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034371427804209</v>
+        <v>-5.032790275344424</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9508855840585837</v>
+        <v>0.9515180450424978</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1745684285534504</v>
+        <v>0.1762139999792503</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.069731636626085</v>
+        <v>3.070718979481565</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.925566542324482</v>
+        <v>-4.923985389864697</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9914056094704682</v>
+        <v>0.9920380704543823</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1745684285534504</v>
+        <v>0.1762139999792503</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.066729707846079</v>
+        <v>3.067717050701559</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.705545744287472</v>
+        <v>-4.703964591827686</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.080992965695887</v>
+        <v>1.081625426679801</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3157882736214306</v>
+        <v>0.3174338450472305</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.153040651897481</v>
+        <v>3.154027994752961</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.572678055224194</v>
+        <v>-4.571096902764409</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.150034224123021</v>
+        <v>1.150666685106935</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3157882736214306</v>
+        <v>0.3174338450472305</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.168934834699304</v>
+        <v>3.169922177554784</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.452504971859695</v>
+        <v>-4.45092381939991</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.199249301909122</v>
+        <v>1.199881762893036</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4359613569859296</v>
+        <v>0.4376069284117295</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.242184529158306</v>
+        <v>3.243171872013785</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.307832826759958</v>
+        <v>-4.306251674300173</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.267206262510457</v>
+        <v>1.267838723494371</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.580633502085667</v>
+        <v>0.5822790735114669</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.339075918779588</v>
+        <v>3.340063261635068</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36770765411765</v>
+        <v>-4.366126501657865</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.229293822968806</v>
+        <v>1.22992628395272</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5207586747279749</v>
+        <v>0.5224042461537748</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.289188513766399</v>
+        <v>3.290175856621878</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.247887423206813</v>
+        <v>-4.246306270747028</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.292511084567349</v>
+        <v>1.293143545551263</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5207586747279749</v>
+        <v>0.5224042461537748</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.304477683000607</v>
+        <v>3.305465025856087</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.250357129668619</v>
+        <v>-4.248775977208834</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.199167401305068</v>
+        <v>1.199799862288982</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5182889682661687</v>
+        <v>0.5199345396919686</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.210640058445965</v>
+        <v>3.211627401301445</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.318727315992629</v>
+        <v>-4.317146163532844</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.091081188260766</v>
+        <v>1.09171364924468</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.5292102387281835</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.135467339352995</v>
+        <v>3.136454682208475</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.332515368839676</v>
+        <v>-4.330934216379891</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.076002675753838</v>
+        <v>1.076635136737752</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.5292102387281835</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.125904047984887</v>
+        <v>3.126891390840366</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.388035444732266</v>
+        <v>-4.386454292272481</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.190825482089005</v>
+        <v>1.191457943072919</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.5292102387281835</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.262934884677089</v>
+        <v>3.263922227532569</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.212561184939796</v>
+        <v>-4.210980032480011</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.265582417997781</v>
+        <v>1.266214878981695</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.5292102387281835</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.267502116668877</v>
+        <v>3.268489459524357</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.323497437581045</v>
+        <v>-4.32191628512126</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.196949945702488</v>
+        <v>1.197582406686402</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5275646673023836</v>
+        <v>0.5292102387281835</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.243244145430084</v>
+        <v>3.244231488285564</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.289833892108763</v>
+        <v>-4.288252739648978</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.138953677292851</v>
+        <v>1.139586138276765</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.5628737842004654</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.191980586114902</v>
+        <v>3.192967928970383</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.229981272905039</v>
+        <v>-4.228400120445254</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.173067111406472</v>
+        <v>1.173699572390386</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.5628737842004654</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.202152972547035</v>
+        <v>3.203140315402515</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.143737809878662</v>
+        <v>-4.142156657418877</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.202510767190884</v>
+        <v>1.203143228174798</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5612282127746655</v>
+        <v>0.5628737842004654</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.197099243120896</v>
+        <v>3.198086585976375</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.189044629277642</v>
+        <v>-4.187463476817856</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.176163814875817</v>
+        <v>1.176796275859731</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5204180497654347</v>
+        <v>0.5220636211912346</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.164388920759882</v>
+        <v>3.165376263615362</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.218077733979943</v>
+        <v>-4.216496581520158</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.165102446027999</v>
+        <v>1.165734907011913</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5204180497654347</v>
+        <v>0.5220636211912346</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.164940793792984</v>
+        <v>3.165928136648464</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.125267252529083</v>
+        <v>-4.123686100069298</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.131499330499708</v>
+        <v>1.132131791483622</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6132285312162941</v>
+        <v>0.614874102642094</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.149899774554865</v>
+        <v>3.150887117410345</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.169656721858511</v>
+        <v>-4.168075569398725</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.115617018692538</v>
+        <v>1.116249479676452</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5688390618868664</v>
+        <v>0.5704846333126663</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.12513956888181</v>
+        <v>3.126126911737289</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.286198326963853</v>
+        <v>-4.284617174504068</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.064076085162124</v>
+        <v>1.064708546146038</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4522974567815236</v>
+        <v>0.4539430282073235</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.050290314330327</v>
+        <v>3.051277657185807</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.403116273601231</v>
+        <v>-4.172240173321395</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.02280020233784</v>
+        <v>1.115150642449774</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4522974567815236</v>
+        <v>0.4539430282073235</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.055781610160994</v>
+        <v>3.056768953016474</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.430896671502584</v>
+        <v>-4.200020571222748</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.023185244945838</v>
+        <v>1.115535685057772</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4245170588801706</v>
+        <v>0.4261626303059705</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.050610573188721</v>
+        <v>3.051597916044201</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.549277344232722</v>
+        <v>-4.318401243952886</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8141886958544358</v>
+        <v>0.9065391359663701</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.3589447781549943</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.848635581898789</v>
+        <v>2.849622924754269</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.657891422676053</v>
+        <v>-4.427015322396217</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8908927251963088</v>
+        <v>0.9832431653082434</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.3589447781549943</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.968785242617995</v>
+        <v>2.969772585473474</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.622482384427911</v>
+        <v>-4.391606284148074</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.919569366597889</v>
+        <v>1.011919806709824</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3572992067291944</v>
+        <v>0.3589447781549943</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.983298268720318</v>
+        <v>2.984285611575797</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.58409872186976</v>
+        <v>-4.353222621589923</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9323422729635182</v>
+        <v>1.024692713075453</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3956828692873455</v>
+        <v>0.3973284407131454</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.003747907597577</v>
+        <v>3.004735250453057</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.406982391834593</v>
+        <v>-4.176106291554757</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9999178338228865</v>
+        <v>1.092268273934821</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3956828692873455</v>
+        <v>0.3973284407131454</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.000476936442879</v>
+        <v>3.001464279298359</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.452074636668139</v>
+        <v>-4.221198536388303</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9825643276513814</v>
+        <v>1.074914767763316</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3337868261179557</v>
+        <v>0.3354323975437556</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.964022702303158</v>
+        <v>2.965010045158638</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.272699215429371</v>
+        <v>-4.041823115149535</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.048101471453303</v>
+        <v>1.140451911565237</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4905635842886744</v>
+        <v>0.4922091557144743</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.051875732512003</v>
+        <v>3.052863075367483</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.317713428949977</v>
+        <v>-4.086837328670141</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.01090324137665</v>
+        <v>1.103253681488585</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4602146889740698</v>
+        <v>0.4618602603998697</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.01447385065483</v>
+        <v>3.015461193510311</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.584717939222412</v>
+        <v>-4.353841838942576</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9097929996066219</v>
+        <v>1.002143439718556</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2658516509311212</v>
+        <v>0.2674972223569211</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.903547590168007</v>
+        <v>2.904534933023487</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.685915720659585</v>
+        <v>-4.455039620379749</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8685178089282544</v>
+        <v>0.9608682490401887</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.197442837385802</v>
+        <v>0.1990884088116019</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.861706223937317</v>
+        <v>2.862693566792797</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.679404754045272</v>
+        <v>-4.448528653765436</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8687221571282961</v>
+        <v>0.9610725972402305</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.197442837385802</v>
+        <v>0.1990884088116019</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.859306185491634</v>
+        <v>2.860293528347114</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.660366626337975</v>
+        <v>-4.429490526058139</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8728621274194599</v>
+        <v>0.9652125675313945</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1392592260546075</v>
+        <v>0.1409047974804074</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.820920737901162</v>
+        <v>2.821908080756642</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.691493257488593</v>
+        <v>-4.460617157208757</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9797058765934028</v>
+        <v>1.072056316705337</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1392592260546075</v>
+        <v>0.1409047974804074</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.940215139535352</v>
+        <v>2.941202482390832</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.83669747342073</v>
+        <v>-4.474483918542675</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9224575192066817</v>
+        <v>1.067342941157904</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.09587756060435393</v>
+        <v>0.1030468807465845</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.915019469251334</v>
+        <v>2.919321061336672</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.7918933018808</v>
+        <v>-4.429679747002745</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9463877182195797</v>
+        <v>1.091273140170802</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.09587756060435393</v>
+        <v>0.1030468807465845</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.92102799964826</v>
+        <v>2.925329591733598</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.644150331645798</v>
+        <v>-4.281936776767743</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9034351275907802</v>
+        <v>1.048320549542002</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2636849178392371</v>
+        <v>0.2708542379814676</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.919662635266389</v>
+        <v>2.923964227351727</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.727971552920496</v>
+        <v>-4.365757998042441</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8727002606123817</v>
+        <v>1.017585682563604</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2636849178392371</v>
+        <v>0.2708542379814676</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.92245625679787</v>
+        <v>2.926757848883208</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.721818846867712</v>
+        <v>-4.359605291989657</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8758236914251538</v>
+        <v>1.020709113376376</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2698376238920214</v>
+        <v>0.2770069440342519</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.926810228821199</v>
+        <v>2.931111820906537</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.738628145018214</v>
+        <v>-4.376414590140159</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8681804489050633</v>
+        <v>1.013065870856285</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2530283257415197</v>
+        <v>0.2601976458837503</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.915805126671008</v>
+        <v>2.920106718756347</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.676330146242091</v>
+        <v>-4.314116591364036</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9594352022123331</v>
+        <v>1.104320624163555</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2530283257415197</v>
+        <v>0.2601976458837503</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.982140680467829</v>
+        <v>2.986442272553167</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.474539948576933</v>
+        <v>-4.112326393698878</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8424432829925235</v>
+        <v>0.9873287049437454</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4510465179106741</v>
+        <v>0.4582158380529047</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.903243597483449</v>
+        <v>2.907545189568787</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.525426661263128</v>
+        <v>-4.163213106385073</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8923788302402207</v>
+        <v>1.037264252191443</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4001598052244796</v>
+        <v>0.4073291253667101</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.943001802193908</v>
+        <v>2.947303394279245</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.623167205888103</v>
+        <v>-4.260953651010047</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8679103485062747</v>
+        <v>1.012795770457497</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3842705270914994</v>
+        <v>0.3914398472337299</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.948095971430163</v>
+        <v>2.952397563515501</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.683376503893387</v>
+        <v>-4.321162949015332</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8423626101288324</v>
+        <v>0.9872480320800543</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3240612290862149</v>
+        <v>0.3312305492284454</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.910506373451664</v>
+        <v>2.914807965537002</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.606954457461461</v>
+        <v>-4.244740902583406</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8714230467415316</v>
+        <v>1.016308468692754</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3240612290862149</v>
+        <v>0.3312305492284454</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.908997991491592</v>
+        <v>2.913299583576931</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.562581325822892</v>
+        <v>-4.200367770944837</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8890351668323953</v>
+        <v>1.033920588783617</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3684343607247835</v>
+        <v>0.375603680867014</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.93548473791017</v>
+        <v>2.939786329995508</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.585061676681777</v>
+        <v>-4.222848121803722</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8744368206274318</v>
+        <v>1.019322242578654</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3684343607247835</v>
+        <v>0.375603680867014</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.92987853204876</v>
+        <v>2.934180124134099</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.537405946120721</v>
+        <v>-4.175192391242666</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8998808698796588</v>
+        <v>1.044766291830881</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4160900912858391</v>
+        <v>0.4232594114280697</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.964853727413198</v>
+        <v>2.969155319498537</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.436887787621966</v>
+        <v>-4.074674232743911</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9449805066538854</v>
+        <v>1.089865928605108</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5166082497845936</v>
+        <v>0.5237775699268242</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.030056995887176</v>
+        <v>3.034358587972514</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.497554378024356</v>
+        <v>-4.135340823146301</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9074685429688019</v>
+        <v>1.052353964920024</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.43490993306606</v>
+        <v>0.4420792532082906</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.967792678331928</v>
+        <v>2.972094270417266</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.452715976415957</v>
+        <v>-4.090502421537902</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9295016062227899</v>
+        <v>1.074387028174012</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4394533660109294</v>
+        <v>0.44662268615316</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.974616440709478</v>
+        <v>2.978918032794816</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917052</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.472214432657966</v>
+        <v>-4.11000087777991</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9258631633570646</v>
+        <v>1.070748585308287</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3913687247310251</v>
+        <v>0.3985380448732557</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.949926595572613</v>
+        <v>2.954228187657952</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.428011595572065</v>
+        <v>-4.06579804069401</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.949423900719262</v>
+        <v>1.094309322670484</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4355715618169256</v>
+        <v>0.4427408819591562</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.982327900351991</v>
+        <v>2.986629492437329</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.464990623235508</v>
+        <v>-4.102777068357453</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9330422901231323</v>
+        <v>1.077927712074354</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4725454636082561</v>
+        <v>0.4797147837504867</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.002922241896037</v>
+        <v>3.007223833981375</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.306699205696236</v>
+        <v>-3.94448565081818</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.047606622321881</v>
+        <v>1.192492044273103</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4725454636082561</v>
+        <v>0.4797147837504867</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.054170007079076</v>
+        <v>3.058471599164415</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.099057202061759</v>
+        <v>-3.736843647183704</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.129104128369925</v>
+        <v>1.273989550321147</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6801874672427323</v>
+        <v>0.6873567873849629</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.177195913854015</v>
+        <v>3.181497505939354</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.048025109339232</v>
+        <v>-3.685811554461176</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.144465193697206</v>
+        <v>1.289350615648428</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7312195599652602</v>
+        <v>0.7383888801074908</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.202763397725802</v>
+        <v>3.207064989811141</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.982800928212026</v>
+        <v>-3.62058737333397</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.187742270240793</v>
+        <v>1.332627692192015</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7964437410924659</v>
+        <v>0.8036130612346964</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.259085310494831</v>
+        <v>3.263386902580169</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.945373908140893</v>
+        <v>-3.583160353262837</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.198674050568526</v>
+        <v>1.343559472519749</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8016952791216475</v>
+        <v>0.8088645992638781</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.25819720561162</v>
+        <v>3.262498797696958</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.965485564175601</v>
+        <v>-3.603272009297545</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.191886180485884</v>
+        <v>1.336771602437106</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8127226241190667</v>
+        <v>0.8198919442612973</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.266070404941312</v>
+        <v>3.27037199702665</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.911740749748396</v>
+        <v>-3.54952719487034</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.373941877277976</v>
+        <v>1.518827299229199</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8227859335595287</v>
+        <v>0.8299552537017593</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.432666161626799</v>
+        <v>3.436967753712138</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.836958488723384</v>
+        <v>-3.474744933845328</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.523967690905798</v>
+        <v>1.668853112857021</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8975681945845413</v>
+        <v>0.9047375147267719</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.597648427459624</v>
+        <v>3.601950019544963</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.810874404459576</v>
+        <v>-3.44866084958152</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.526109300625181</v>
+        <v>1.670994722576403</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8975681945845413</v>
+        <v>0.9047375147267719</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.589356403473483</v>
+        <v>3.593657995558821</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.732743223610629</v>
+        <v>-3.370529668732573</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.555554968548539</v>
+        <v>1.700440390499761</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9717450054682258</v>
+        <v>0.9789143256104564</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.632055685587473</v>
+        <v>3.636357277672812</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.723850762217346</v>
+        <v>-3.36163720733929</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.576666358832643</v>
+        <v>1.721551780783866</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9717450054682258</v>
+        <v>0.9789143256104564</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.649610091314265</v>
+        <v>3.653911683399603</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.892326879187224</v>
+        <v>-3.530113324309168</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.501130959449276</v>
+        <v>1.646016381400499</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9437971697516451</v>
+        <v>0.9509664898938757</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.6246964372889</v>
+        <v>3.628998029374239</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.19452735032564</v>
+        <v>-2.832313795447584</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.761520468181771</v>
+        <v>1.906405890132994</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8734491103812343</v>
+        <v>0.880618430523465</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.563757298854516</v>
+        <v>3.568058890939854</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.171806246642488</v>
+        <v>-2.809592691764432</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.761272932151937</v>
+        <v>1.906158354103159</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8734491103812343</v>
+        <v>0.880618430523465</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.55442132135142</v>
+        <v>3.558722913436759</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.30100805993653</v>
+        <v>-2.938794505058474</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.868498332685489</v>
+        <v>2.013383754636711</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7442472970871921</v>
+        <v>0.7514166172294228</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.635806359226164</v>
+        <v>3.640107951311502</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.455789066714786</v>
+        <v>-3.09357551183673</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.843663752467833</v>
+        <v>1.988549174419056</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7108796230327159</v>
+        <v>0.7180489431749466</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.652863577287125</v>
+        <v>3.657165169372463</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799966</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.448734376499612</v>
+        <v>-3.086520821621556</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.843160984543448</v>
+        <v>1.988046406494671</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7179343132478897</v>
+        <v>0.7251036333901204</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.653771747405774</v>
+        <v>3.658073339491112</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.421783152173124</v>
+        <v>-3.059569597295068</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.863947627918785</v>
+        <v>2.008833049870007</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7328146592756088</v>
+        <v>0.7399839794178396</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.672706108667147</v>
+        <v>3.677007700752486</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.557736160229441</v>
+        <v>-3.195522605351385</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.993669556841218</v>
+        <v>2.13855497879244</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7328146592756088</v>
+        <v>0.7399839794178396</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.856809240812107</v>
+        <v>3.861110832897445</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714428</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.580144278034313</v>
+        <v>-3.217930723156257</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.976823004622262</v>
+        <v>2.121708426573485</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7328146592756088</v>
+        <v>0.7399839794178396</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.8489259357151</v>
+        <v>3.853227527800438</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.728150045513712</v>
+        <v>-3.365936490635656</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.91967469718014</v>
+        <v>2.064560119131362</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6460876504120674</v>
+        <v>0.6532569705542981</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.798943729946612</v>
+        <v>3.803245322031951</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.913137467117562</v>
+        <v>-3.375377416524186</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.901933446260447</v>
+        <v>2.117037466497798</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.5933901999840563</v>
+        <v>0.7756840880976895</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.823578977411653</v>
+        <v>3.932955310279833</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.965411074453204</v>
+        <v>-3.427651023859827</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.883915097871491</v>
+        <v>2.099019118108842</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.5411165926484151</v>
+        <v>0.7234104807620483</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.795105907555569</v>
+        <v>3.904482240423749</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-4.041741052054109</v>
+        <v>-3.503981001460733</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.851494919724904</v>
+        <v>2.066598939962255</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.5411165926484151</v>
+        <v>0.7234104807620483</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.793217720449344</v>
+        <v>3.902594053317524</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-4.243994772378463</v>
+        <v>-3.706234721785087</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.765413661198025</v>
+        <v>1.980517681435376</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3388628723240616</v>
+        <v>0.5211567604376948</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.666685717857595</v>
+        <v>3.776062050725775</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.405563197905718</v>
+        <v>-3.867803147312342</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.699220301197275</v>
+        <v>1.914324321434626</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.2120799485261822</v>
+        <v>0.3943738366398154</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.589049973789019</v>
+        <v>3.698426306657199</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647108</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.537864490003272</v>
+        <v>-4.000104439409895</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.659373191224172</v>
+        <v>1.874477211461523</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.2120799485261822</v>
+        <v>0.3943738366398154</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.602123380654938</v>
+        <v>3.711499713523118</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763536</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.539426132818131</v>
+        <v>-4.001666082224755</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.658748534098229</v>
+        <v>1.873852554335579</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.2120799485261822</v>
+        <v>0.3943738366398154</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.602123380654938</v>
+        <v>3.711499713523118</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392119</v>
+        <v>3.715834055392114</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.567326919927604</v>
+        <v>-4.029566869334228</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.646112260381442</v>
+        <v>1.861216280618792</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.1774830243832474</v>
+        <v>0.3597769124968806</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.579889267296179</v>
+        <v>3.689265600164359</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68490993917253</v>
+        <v>3.684909939172525</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.689853022630498</v>
+        <v>-4.152092972037122</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.593866263277483</v>
+        <v>1.808970283514833</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.05495692168035354</v>
+        <v>0.2372508097939867</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.503138049651642</v>
+        <v>3.612514382519822</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971076</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.920367518816087</v>
+        <v>-4.382607468222711</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.568366424393751</v>
+        <v>1.783470444631101</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.1755575745052352</v>
+        <v>0.006736313608397992</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.431535311530792</v>
+        <v>3.540911644398972</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199808</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-5.177088336810911</v>
+        <v>-4.639328286217534</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.605989816197668</v>
+        <v>1.821093836435019</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.28397214864905</v>
+        <v>-0.1016782605354168</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.50679828604635</v>
+        <v>3.61617461891453</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.331074754587052</v>
+        <v>-4.793314703993675</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.613375518232852</v>
+        <v>1.828479538470203</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.28397214864905</v>
+        <v>-0.1016782605354168</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.57577855519199</v>
+        <v>3.68515488806017</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61993717680853</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.280552850759386</v>
+        <v>-4.742792800166009</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.619635481884039</v>
+        <v>1.83473950212139</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.28397214864905</v>
+        <v>-0.1016782605354168</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.561829757312111</v>
+        <v>3.671206090180291</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.53302800476711</v>
+        <v>-4.995267954173733</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.530515909336363</v>
+        <v>1.745619929573714</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.28397214864905</v>
+        <v>-0.1016782605354168</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.573700246367525</v>
+        <v>3.683076579235705</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.6740426963583</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.802500806688818</v>
+        <v>-5.264740756095441</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.423937323086624</v>
+        <v>1.639041343323975</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.28397214864905</v>
+        <v>-0.1016782605354168</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.574910780886468</v>
+        <v>3.684287113754649</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637089</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.96004487841826</v>
+        <v>-5.422284827824883</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.365041436622168</v>
+        <v>1.580145456859519</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.3508739537893245</v>
+        <v>-0.1685800656756913</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.538891440029625</v>
+        <v>3.648267772897805</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301345</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-6.238009274001533</v>
+        <v>-5.700249223408156</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.248933531125048</v>
+        <v>1.4640375513624</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.4404936880748088</v>
+        <v>-0.2581997999611756</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.480197452194524</v>
+        <v>3.589573785062704</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215472</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.354976966640424</v>
+        <v>-5.817216916047047</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.364350510768536</v>
+        <v>1.579454531005887</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.4404936880748088</v>
+        <v>-0.2581997999611756</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.642401508893568</v>
+        <v>3.751777841761748</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456694</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.439694908861378</v>
+        <v>-5.901934858268</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.325309971843969</v>
+        <v>1.54041399208132</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.5256097170028551</v>
+        <v>-0.343315828889222</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.586178529500555</v>
+        <v>3.695554862368735</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253289</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.521629727130261</v>
+        <v>-5.983869676536884</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.302765462104907</v>
+        <v>1.517869482342258</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.5355444625899353</v>
+        <v>-0.3532505744763021</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.590447099716798</v>
+        <v>3.699823432584977</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717834</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.623605849378668</v>
+        <v>-6.085845798785291</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.270900651661446</v>
+        <v>1.486004671898797</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.6375205848383428</v>
+        <v>-0.4552266967247097</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.538187064823656</v>
+        <v>3.647563397691835</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616951</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.513599565901447</v>
+        <v>-5.97583951530807</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.30705605229651</v>
+        <v>1.522160072533861</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.6143160129210676</v>
+        <v>-0.4320221248074345</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.544262695218196</v>
+        <v>3.653639028086376</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203666</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.370539990160522</v>
+        <v>-5.832779939567144</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.368529893314855</v>
+        <v>1.583633913552206</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.6063025863310884</v>
+        <v>-0.4240086982174552</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.553320761894158</v>
+        <v>3.662697094762338</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436931</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-6.069093264688684</v>
+        <v>-5.531333214095307</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.496369466386126</v>
+        <v>1.711473486623477</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.3048558608592511</v>
+        <v>-0.122561972745618</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.741449680059796</v>
+        <v>3.850826012927976</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064768</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-6.093683508923868</v>
+        <v>-5.555923458330491</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.487504546444762</v>
+        <v>1.702608566682113</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.3048558608592511</v>
+        <v>-0.122561972745618</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.742420857812506</v>
+        <v>3.851797190680686</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859302</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-6.042645132917348</v>
+        <v>-5.569802206351264</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.508762801227126</v>
+        <v>1.697899971853559</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.3048558608592511</v>
+        <v>-0.122561972745618</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.743263762192262</v>
+        <v>3.852640095060442</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354685</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-6.001505838050717</v>
+        <v>-5.528662911484633</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.544256618047924</v>
+        <v>1.733393788674357</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.2637165659926203</v>
+        <v>-0.08142267787898716</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.786985437986386</v>
+        <v>3.896361770854566</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085621</v>
+        <v>3.825767093085619</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.890899697971115</v>
+        <v>-5.418056771405031</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.404683070203699</v>
+        <v>1.593820240830133</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.1531104259130183</v>
+        <v>0.02918346220061485</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.669533118158082</v>
+        <v>3.778909451026262</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462783</v>
+        <v>3.804703121462781</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-6.021480432501957</v>
+        <v>-5.548637505935874</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.355952820465326</v>
+        <v>1.545089991091759</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.2836911604438608</v>
+        <v>-0.1013972723302277</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.59468672151354</v>
+        <v>3.70406305438172</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.7750430212186</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.856984098310996</v>
+        <v>-5.384141171744912</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.406178173217793</v>
+        <v>1.595315343844227</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.2836911604438608</v>
+        <v>-0.1013972723302277</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.579113540589622</v>
+        <v>3.688489873457802</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462771</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.732503617587044</v>
+        <v>-5.259660691020961</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.455158075943804</v>
+        <v>1.644295246570237</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.2836911604438608</v>
+        <v>-0.1013972723302277</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.578301251026052</v>
+        <v>3.687677583894232</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533052</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.742666578201193</v>
+        <v>-5.27004588591085</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.460961670823216</v>
+        <v>1.650009947739353</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.2938541210580104</v>
+        <v>-0.111782467220117</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.582072253782635</v>
+        <v>3.691315246085371</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120425</v>
+        <v>3.834429654120423</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.651912102172552</v>
+        <v>-5.179291409882208</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.568100467011098</v>
+        <v>1.757148743927235</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.2030996450293687</v>
+        <v>-0.02102799119147525</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.707361945176245</v>
+        <v>3.816604937478981</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881701</v>
+        <v>3.8551346958817</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.510195354358147</v>
+        <v>-5.037574662067803</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.621656176955158</v>
+        <v>1.810704453871296</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.2030996450293687</v>
+        <v>-0.02102799119147525</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.704230955994543</v>
+        <v>3.813473948297279</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.807495453259816</v>
+        <v>3.859491728260294</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.393054335571869</v>
+        <v>-5.060299618020089</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.673043479409061</v>
+        <v>1.806145366429773</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.08595862624309109</v>
+        <v>-0.0437529471437611</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.779046462205701</v>
+        <v>3.8043698696653</v>
       </c>
     </row>
   </sheetData>
